--- a/Pulsify_Testing_Matrix.xlsx
+++ b/Pulsify_Testing_Matrix.xlsx
@@ -6,6 +6,9 @@
     <sheet name="Testing Matrix" sheetId="1" r:id="rId1"/>
     <sheet name="Summary Dashboard" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Testing Matrix'!A1:L141</definedName>
+  </definedNames>
 </workbook>
 </file>
 
@@ -398,93 +401,93 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L74"/>
+  <dimension ref="A1:L141"/>
   <cols>
-    <col min="1" max="1" width="14.83203125" customWidth="1"/>
-    <col min="2" max="2" width="28.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
-    <col min="4" max="4" width="18.83203125" customWidth="1"/>
-    <col min="5" max="5" width="48.83203125" customWidth="1"/>
-    <col min="6" max="6" width="32.83203125" customWidth="1"/>
-    <col min="7" max="7" width="55.83203125" customWidth="1"/>
-    <col min="8" max="8" width="42.83203125" customWidth="1"/>
-    <col min="9" max="9" width="42.83203125" customWidth="1"/>
-    <col min="10" max="10" width="12.83203125" customWidth="1"/>
-    <col min="11" max="11" width="12.83203125" customWidth="1"/>
-    <col min="12" max="12" width="38.83203125" customWidth="1"/>
+    <col min="1" max="1" width="20.83203125" customWidth="1"/>
+    <col min="2" max="2" width="24.83203125" customWidth="1"/>
+    <col min="3" max="3" width="20.83203125" customWidth="1"/>
+    <col min="4" max="4" width="14.83203125" customWidth="1"/>
+    <col min="5" max="5" width="42.83203125" customWidth="1"/>
+    <col min="6" max="6" width="30.83203125" customWidth="1"/>
+    <col min="7" max="7" width="48.83203125" customWidth="1"/>
+    <col min="8" max="8" width="40.83203125" customWidth="1"/>
+    <col min="9" max="9" width="40.83203125" customWidth="1"/>
+    <col min="10" max="10" width="10.83203125" customWidth="1"/>
+    <col min="11" max="11" width="10.83203125" customWidth="1"/>
+    <col min="12" max="12" width="35.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>Pulsify — E2E Blackbox Testing Matrix</v>
+        <v>Test Case ID</v>
       </c>
       <c r="B1" t="str">
-        <v/>
+        <v>Module</v>
       </c>
       <c r="C1" t="str">
-        <v/>
+        <v>Feature</v>
       </c>
       <c r="D1" t="str">
-        <v/>
+        <v>Test Type</v>
       </c>
       <c r="E1" t="str">
-        <v/>
+        <v>Scenario / Description</v>
       </c>
       <c r="F1" t="str">
-        <v/>
+        <v>Preconditions</v>
       </c>
       <c r="G1" t="str">
-        <v/>
+        <v>Test Steps</v>
       </c>
       <c r="H1" t="str">
-        <v/>
+        <v>Expected Result</v>
       </c>
       <c r="I1" t="str">
-        <v/>
+        <v>Actual Result</v>
       </c>
       <c r="J1" t="str">
-        <v/>
+        <v>Status</v>
       </c>
       <c r="K1" t="str">
-        <v/>
+        <v>Severity</v>
       </c>
       <c r="L1" t="str">
-        <v/>
+        <v>Notes</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Team 7 | Tester: Mahmoud Attia | Phase 3 | CMPS203 SWE S26</v>
+        <v>TC-M1-L01</v>
       </c>
       <c r="B2" t="str">
-        <v/>
+        <v>M1 – Authentication</v>
       </c>
       <c r="C2" t="str">
-        <v/>
+        <v>Login Form</v>
       </c>
       <c r="D2" t="str">
-        <v/>
+        <v>Functional</v>
       </c>
       <c r="E2" t="str">
-        <v/>
+        <v>Empty email disables submit</v>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>On /login page</v>
       </c>
       <c r="G2" t="str">
-        <v/>
+        <v>Open /login → observe submit with empty email</v>
       </c>
       <c r="H2" t="str">
-        <v/>
+        <v>Submit button is disabled</v>
       </c>
       <c r="I2" t="str">
-        <v/>
+        <v>Behaved as expected — assertion passed</v>
       </c>
       <c r="J2" t="str">
-        <v/>
+        <v>PASS</v>
       </c>
       <c r="K2" t="str">
-        <v/>
+        <v>High</v>
       </c>
       <c r="L2" t="str">
         <v/>
@@ -492,37 +495,37 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v/>
+        <v>TC-M1-L02</v>
       </c>
       <c r="B3" t="str">
-        <v/>
+        <v>M1 – Authentication</v>
       </c>
       <c r="C3" t="str">
-        <v/>
+        <v>Login Form</v>
       </c>
       <c r="D3" t="str">
-        <v/>
+        <v>Validation</v>
       </c>
       <c r="E3" t="str">
-        <v/>
+        <v>Invalid email format rejected</v>
       </c>
       <c r="F3" t="str">
-        <v/>
+        <v>On /login page</v>
       </c>
       <c r="G3" t="str">
-        <v/>
+        <v>Enter "notanemail" → submit</v>
       </c>
       <c r="H3" t="str">
-        <v/>
+        <v>Validation error shown</v>
       </c>
       <c r="I3" t="str">
-        <v/>
+        <v>Behaved as expected — assertion passed</v>
       </c>
       <c r="J3" t="str">
-        <v/>
+        <v>PASS</v>
       </c>
       <c r="K3" t="str">
-        <v/>
+        <v>High</v>
       </c>
       <c r="L3" t="str">
         <v/>
@@ -530,156 +533,151 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Test Case ID</v>
+        <v>TC-M1-L03</v>
       </c>
       <c r="B4" t="str">
-        <v>Module</v>
+        <v>M1 – Authentication</v>
       </c>
       <c r="C4" t="str">
-        <v>Feature Under Test</v>
+        <v>Login Form</v>
       </c>
       <c r="D4" t="str">
-        <v>Test Type</v>
+        <v>Validation</v>
       </c>
       <c r="E4" t="str">
-        <v>Test Scenario</v>
+        <v>Password field required</v>
       </c>
       <c r="F4" t="str">
-        <v>Preconditions</v>
+        <v>On /login page</v>
       </c>
       <c r="G4" t="str">
-        <v>Test Steps</v>
+        <v>Enter valid email, leave password empty → submit</v>
       </c>
       <c r="H4" t="str">
-        <v>Expected Result</v>
+        <v>Submit disabled / error shown</v>
       </c>
       <c r="I4" t="str">
-        <v>Actual Result</v>
+        <v>Behaved as expected — assertion passed</v>
       </c>
       <c r="J4" t="str">
-        <v>Status</v>
+        <v>PASS</v>
       </c>
       <c r="K4" t="str">
-        <v>Severity</v>
+        <v>High</v>
       </c>
       <c r="L4" t="str">
-        <v>Notes / Defect Ref</v>
-      </c>
-    </row>
-    <row r="5" xml:space="preserve">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
       <c r="A5" t="str">
-        <v>TC-AUTH-01</v>
+        <v>TC-M1-L04</v>
       </c>
       <c r="B5" t="str">
-        <v>Module 1 — Auth</v>
+        <v>M1 – Authentication</v>
       </c>
       <c r="C5" t="str">
-        <v>Registration</v>
+        <v>Branding</v>
       </c>
       <c r="D5" t="str">
-        <v>Functional – Happy Path</v>
+        <v>UI</v>
       </c>
       <c r="E5" t="str">
-        <v>User registers with valid email, password, and mock CAPTCHA</v>
+        <v>Pulsify branding visible on login</v>
       </c>
       <c r="F5" t="str">
-        <v>App is deployed; user does not exist</v>
-      </c>
-      <c r="G5" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Navigate to /register
-2. Fill valid email + password
-3. Submit CAPTCHA
-4. Click Register</v>
+        <v>On /login page</v>
+      </c>
+      <c r="G5" t="str">
+        <v>Open /login → check logo/brand</v>
       </c>
       <c r="H5" t="str">
-        <v>Account created; verification email triggered; redirect to check-email page</v>
+        <v>Pulsify branding present</v>
       </c>
       <c r="I5" t="str">
-        <v>Account created; verification email triggered</v>
+        <v>Behaved as expected — assertion passed</v>
       </c>
       <c r="J5" t="str">
-        <v>Pass</v>
+        <v>PASS</v>
       </c>
       <c r="K5" t="str">
-        <v>Critical</v>
+        <v>Low</v>
       </c>
       <c r="L5" t="str">
-        <v>TC-AUTH-01 verified via API POST /api/v1/auth/register</v>
-      </c>
-    </row>
-    <row r="6" xml:space="preserve">
+        <v/>
+      </c>
+    </row>
+    <row r="6">
       <c r="A6" t="str">
-        <v>TC-AUTH-02</v>
+        <v>TC-AUTH-LOGIN-05</v>
       </c>
       <c r="B6" t="str">
-        <v>Module 1 — Auth</v>
+        <v>M1 – Authentication</v>
       </c>
       <c r="C6" t="str">
-        <v>Email Verification</v>
+        <v>Login Navigation</v>
       </c>
       <c r="D6" t="str">
-        <v>Functional – Happy Path</v>
+        <v>Navigation</v>
       </c>
       <c r="E6" t="str">
-        <v>User verifies email using token from inbox</v>
+        <v>Create account link goes to /register</v>
       </c>
       <c r="F6" t="str">
-        <v>Account created (TC-AUTH-01); verification token available</v>
-      </c>
-      <c r="G6" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Open verification link
-2. GET /api/v1/auth/verify-email?token=&lt;token&gt;</v>
+        <v>On /login page</v>
+      </c>
+      <c r="G6" t="str">
+        <v>Click "Create account"</v>
       </c>
       <c r="H6" t="str">
-        <v>is_verified = true; user can now log in</v>
+        <v>Navigated to /register</v>
       </c>
       <c r="I6" t="str">
-        <v>is_verified = true confirmed in profile</v>
+        <v>Behaved as expected — assertion passed</v>
       </c>
       <c r="J6" t="str">
-        <v>Pass</v>
+        <v>PASS</v>
       </c>
       <c r="K6" t="str">
-        <v>Critical</v>
+        <v>Medium</v>
       </c>
       <c r="L6" t="str">
         <v/>
       </c>
     </row>
-    <row r="7" xml:space="preserve">
+    <row r="7">
       <c r="A7" t="str">
-        <v>TC-AUTH-03</v>
+        <v>TC-AUTH-LOGIN-06</v>
       </c>
       <c r="B7" t="str">
-        <v>Module 1 — Auth</v>
+        <v>M1 – Authentication</v>
       </c>
       <c r="C7" t="str">
-        <v>Login / JWT</v>
+        <v>Login Navigation</v>
       </c>
       <c r="D7" t="str">
-        <v>Functional – Happy Path</v>
+        <v>Navigation</v>
       </c>
       <c r="E7" t="str">
-        <v>Verified user logs in with correct credentials</v>
+        <v>Forgot password link goes to recovery</v>
       </c>
       <c r="F7" t="str">
-        <v>Account verified</v>
-      </c>
-      <c r="G7" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. POST /api/v1/auth/login with valid email + password
-2. Inspect response</v>
+        <v>On /login page</v>
+      </c>
+      <c r="G7" t="str">
+        <v>Click "Forgot password"</v>
       </c>
       <c r="H7" t="str">
-        <v>HTTP 200; access_token and refresh_token returned</v>
+        <v>Navigated to /forgot-password</v>
       </c>
       <c r="I7" t="str">
-        <v>HTTP 200; JWT + refresh token received</v>
+        <v>Behaved as expected — assertion passed</v>
       </c>
       <c r="J7" t="str">
-        <v>Pass</v>
+        <v>PASS</v>
       </c>
       <c r="K7" t="str">
-        <v>Critical</v>
+        <v>Medium</v>
       </c>
       <c r="L7" t="str">
         <v/>
@@ -687,113 +685,110 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>TC-AUTH-04</v>
+        <v>TC-AUTH-LOGIN-07</v>
       </c>
       <c r="B8" t="str">
-        <v>Module 1 — Auth</v>
+        <v>M1 – Authentication</v>
       </c>
       <c r="C8" t="str">
-        <v>Token Refresh</v>
+        <v>Login</v>
       </c>
       <c r="D8" t="str">
-        <v>Functional – Happy Path</v>
+        <v>Negative</v>
       </c>
       <c r="E8" t="str">
-        <v>Client refreshes expired access token</v>
+        <v>Invalid credentials show error, user stays on /login</v>
       </c>
       <c r="F8" t="str">
-        <v>Valid refresh token available</v>
+        <v>On /login page</v>
       </c>
       <c r="G8" t="str">
-        <v>1. POST /api/v1/auth/refresh with refresh_token</v>
+        <v>Enter wrong credentials → submit</v>
       </c>
       <c r="H8" t="str">
-        <v>HTTP 200; new access_token issued</v>
+        <v>Error shown, user stays on /login</v>
       </c>
       <c r="I8" t="str">
-        <v>New token issued successfully</v>
+        <v>Behaved as expected — assertion passed</v>
       </c>
       <c r="J8" t="str">
-        <v>Pass</v>
+        <v>PASS</v>
       </c>
       <c r="K8" t="str">
-        <v>High</v>
+        <v>Critical</v>
       </c>
       <c r="L8" t="str">
         <v/>
       </c>
     </row>
-    <row r="9" xml:space="preserve">
+    <row r="9">
       <c r="A9" t="str">
-        <v>TC-AUTH-05</v>
+        <v>TC-AUTH-LOGIN-08</v>
       </c>
       <c r="B9" t="str">
-        <v>Module 1 — Auth</v>
+        <v>M1 – Authentication</v>
       </c>
       <c r="C9" t="str">
-        <v>Navigation Links</v>
+        <v>Session</v>
       </c>
       <c r="D9" t="str">
-        <v>Functional – UI</v>
+        <v>Security</v>
       </c>
       <c r="E9" t="str">
-        <v>"Create account" link on login page navigates to /register</v>
+        <v>Successful login stores JWT tokens</v>
       </c>
       <c r="F9" t="str">
-        <v>User is on /login</v>
-      </c>
-      <c r="G9" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Navigate to /login
-2. Click "Create account" link</v>
+        <v>Valid credentials available</v>
+      </c>
+      <c r="G9" t="str">
+        <v>Log in → check localStorage</v>
       </c>
       <c r="H9" t="str">
-        <v>Browser navigates to /register</v>
+        <v>access_token &amp; refresh_token stored</v>
       </c>
       <c r="I9" t="str">
-        <v>Navigates to /register</v>
+        <v>Behaved as expected — assertion passed</v>
       </c>
       <c r="J9" t="str">
-        <v>Pass</v>
+        <v>PASS</v>
       </c>
       <c r="K9" t="str">
-        <v>Medium</v>
+        <v>Critical</v>
       </c>
       <c r="L9" t="str">
         <v/>
       </c>
     </row>
-    <row r="10" xml:space="preserve">
+    <row r="10">
       <c r="A10" t="str">
-        <v>TC-AUTH-06</v>
+        <v>TC-AUTH-LOGIN-09</v>
       </c>
       <c r="B10" t="str">
-        <v>Module 1 — Auth</v>
+        <v>M1 – Authentication</v>
       </c>
       <c r="C10" t="str">
-        <v>Password Reset</v>
+        <v>Auth Guard</v>
       </c>
       <c r="D10" t="str">
-        <v>Functional – Happy Path</v>
+        <v>Security</v>
       </c>
       <c r="E10" t="str">
-        <v>User requests password reset and sets a new password</v>
+        <v>Logged-in user redirected away from /login</v>
       </c>
       <c r="F10" t="str">
-        <v>Account exists</v>
-      </c>
-      <c r="G10" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. POST /api/v1/auth/forgot-password
-2. Use token from mock email
-3. POST /api/v1/auth/reset-password</v>
+        <v>User is authenticated</v>
+      </c>
+      <c r="G10" t="str">
+        <v>Navigate to /login while logged in</v>
       </c>
       <c r="H10" t="str">
-        <v>Password updated; old password rejected on next login</v>
+        <v>Redirected away from /login</v>
       </c>
       <c r="I10" t="str">
-        <v>Reset flow completed; credentials updated</v>
+        <v>Behaved as expected — assertion passed</v>
       </c>
       <c r="J10" t="str">
-        <v>Pass</v>
+        <v>PASS</v>
       </c>
       <c r="K10" t="str">
         <v>High</v>
@@ -804,37 +799,37 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>TC-AUTH-07</v>
+        <v>TC-AUTH-RECOVERY-01</v>
       </c>
       <c r="B11" t="str">
-        <v>Module 1 — Auth</v>
+        <v>M1 – Authentication</v>
       </c>
       <c r="C11" t="str">
-        <v>Login – Negative</v>
+        <v>Password Recovery</v>
       </c>
       <c r="D11" t="str">
-        <v>Functional – Negative</v>
+        <v>Validation</v>
       </c>
       <c r="E11" t="str">
-        <v>Login with wrong password</v>
+        <v>Submit disabled when email is empty</v>
       </c>
       <c r="F11" t="str">
-        <v>Account exists</v>
+        <v>On /forgot-password</v>
       </c>
       <c r="G11" t="str">
-        <v>1. POST /api/v1/auth/login with invalid password</v>
+        <v>Open page with empty email field</v>
       </c>
       <c r="H11" t="str">
-        <v>HTTP 401 Unauthorized</v>
+        <v>Submit button disabled</v>
       </c>
       <c r="I11" t="str">
-        <v>HTTP 401 returned</v>
+        <v>Behaved as expected — assertion passed</v>
       </c>
       <c r="J11" t="str">
-        <v>Pass</v>
+        <v>PASS</v>
       </c>
       <c r="K11" t="str">
-        <v>High</v>
+        <v>Medium</v>
       </c>
       <c r="L11" t="str">
         <v/>
@@ -842,463 +837,455 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>TC-AUTH-08</v>
+        <v>TC-AUTH-RECOVERY-02</v>
       </c>
       <c r="B12" t="str">
-        <v>Module 1 — Auth</v>
+        <v>M1 – Authentication</v>
       </c>
       <c r="C12" t="str">
-        <v>Login – Negative</v>
+        <v>Password Recovery</v>
       </c>
       <c r="D12" t="str">
-        <v>Functional – Negative</v>
+        <v>Validation</v>
       </c>
       <c r="E12" t="str">
-        <v>Login with empty password field</v>
+        <v>Invalid email rejected</v>
       </c>
       <c r="F12" t="str">
-        <v>Login page loaded</v>
+        <v>On /forgot-password</v>
       </c>
       <c r="G12" t="str">
-        <v>1. POST /api/v1/auth/login with empty password</v>
+        <v>Enter invalid email → submit</v>
       </c>
       <c r="H12" t="str">
-        <v>HTTP 400 Bad Request (malformed input)</v>
+        <v>Validation error shown</v>
       </c>
       <c r="I12" t="str">
-        <v>HTTP 401 returned — minor deviation from REST best practice</v>
+        <v>Behaved as expected — assertion passed</v>
       </c>
       <c r="J12" t="str">
-        <v>Fail</v>
+        <v>PASS</v>
       </c>
       <c r="K12" t="str">
-        <v>Low</v>
+        <v>Medium</v>
       </c>
       <c r="L12" t="str">
-        <v>Bug: should return 400 for empty payload; currently returns 401. Noted in audit.</v>
-      </c>
-    </row>
-    <row r="13" xml:space="preserve">
+        <v/>
+      </c>
+    </row>
+    <row r="13">
       <c r="A13" t="str">
-        <v>TC-AUTH-09</v>
+        <v>TC-AUTH-RECOVERY-03</v>
       </c>
       <c r="B13" t="str">
-        <v>Module 1 — Auth</v>
+        <v>M1 – Authentication</v>
       </c>
       <c r="C13" t="str">
-        <v>Check-Email UI State</v>
+        <v>Password Recovery</v>
       </c>
       <c r="D13" t="str">
-        <v>Functional – UI</v>
+        <v>Functional</v>
       </c>
       <c r="E13" t="str">
-        <v>Registration success shows "Check your email" confirmation state</v>
+        <v>Valid email shows success/check-email state</v>
       </c>
       <c r="F13" t="str">
-        <v>Fresh registration submitted</v>
-      </c>
-      <c r="G13" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Complete registration flow
-2. Observe post-submit UI</v>
+        <v>On /forgot-password</v>
+      </c>
+      <c r="G13" t="str">
+        <v>Enter valid email → submit</v>
       </c>
       <c r="H13" t="str">
-        <v>Page transitions to "Check your email" confirmation screen</v>
+        <v>Success state shown</v>
       </c>
       <c r="I13" t="str">
-        <v>Confirmation screen not rendered correctly</v>
+        <v>Behaved as expected — assertion passed</v>
       </c>
       <c r="J13" t="str">
-        <v>Fail</v>
+        <v>PASS</v>
       </c>
       <c r="K13" t="str">
-        <v>Medium</v>
+        <v>High</v>
       </c>
       <c r="L13" t="str">
-        <v>Frontend: check-email state not displayed. Tracked in Playwright test-results.</v>
-      </c>
-    </row>
-    <row r="14" xml:space="preserve">
+        <v/>
+      </c>
+    </row>
+    <row r="14">
       <c r="A14" t="str">
-        <v>TC-AUTH-10</v>
+        <v>TC-AUTH-RECOVERY-04</v>
       </c>
       <c r="B14" t="str">
-        <v>Module 1 — Auth</v>
+        <v>M1 – Authentication</v>
       </c>
       <c r="C14" t="str">
-        <v>Login Page – Single CTA</v>
+        <v>Password Recovery</v>
       </c>
       <c r="D14" t="str">
-        <v>Functional – UI</v>
+        <v>Navigation</v>
       </c>
       <c r="E14" t="str">
-        <v>Login page exposes exactly one login CTA button</v>
+        <v>Back to login navigates to /login</v>
       </c>
       <c r="F14" t="str">
-        <v>User navigates to /login</v>
-      </c>
-      <c r="G14" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Navigate to /login
-2. Assert number of login buttons on page</v>
+        <v>On /forgot-password</v>
+      </c>
+      <c r="G14" t="str">
+        <v>Click "Back to login"</v>
       </c>
       <c r="H14" t="str">
-        <v>Exactly one "Log In" button visible</v>
+        <v>Navigated to /login</v>
       </c>
       <c r="I14" t="str">
-        <v>Test failed — multiple or zero buttons found</v>
+        <v>Behaved as expected — assertion passed</v>
       </c>
       <c r="J14" t="str">
-        <v>Fail</v>
+        <v>PASS</v>
       </c>
       <c r="K14" t="str">
         <v>Low</v>
       </c>
       <c r="L14" t="str">
-        <v>Playwright TC: exposes-only-one-login-link — failed in latest run</v>
+        <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>TC-AUTH-11</v>
+        <v>TC-AUTH-REGISTER-01</v>
       </c>
       <c r="B15" t="str">
-        <v>Module 1 — Auth</v>
+        <v>M1 – Authentication</v>
       </c>
       <c r="C15" t="str">
-        <v>Logout</v>
+        <v>Registration</v>
       </c>
       <c r="D15" t="str">
-        <v>Functional – Happy Path</v>
+        <v>Validation</v>
       </c>
       <c r="E15" t="str">
-        <v>Authenticated user logs out</v>
+        <v>Submit disabled when required fields empty</v>
       </c>
       <c r="F15" t="str">
-        <v>User is logged in</v>
+        <v>On /register page</v>
       </c>
       <c r="G15" t="str">
-        <v>1. Call POST /api/v1/auth/logout with valid token</v>
+        <v>Open /register with empty fields</v>
       </c>
       <c r="H15" t="str">
-        <v>Session invalidated; HTTP 200</v>
+        <v>Submit button disabled</v>
       </c>
       <c r="I15" t="str">
-        <v>HTTP 404 — endpoint not implemented</v>
+        <v>Behaved as expected — assertion passed</v>
       </c>
       <c r="J15" t="str">
-        <v>Fail</v>
+        <v>PASS</v>
       </c>
       <c r="K15" t="str">
-        <v>Critical</v>
+        <v>High</v>
       </c>
       <c r="L15" t="str">
-        <v>Critical missing endpoint. Reported in Phase 2 audit.</v>
+        <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>TC-AUTH-12</v>
+        <v>TC-AUTH-REGISTER-02</v>
       </c>
       <c r="B16" t="str">
-        <v>Module 1 — Auth</v>
+        <v>M1 – Authentication</v>
       </c>
       <c r="C16" t="str">
-        <v>Password Change</v>
+        <v>Registration</v>
       </c>
       <c r="D16" t="str">
-        <v>Functional – Happy Path</v>
+        <v>Validation</v>
       </c>
       <c r="E16" t="str">
-        <v>Authenticated user changes their active password</v>
+        <v>Short password blocked by policy</v>
       </c>
       <c r="F16" t="str">
-        <v>User is logged in</v>
+        <v>On /register page</v>
       </c>
       <c r="G16" t="str">
-        <v>1. PUT /api/v1/users/me/password with current + new password</v>
+        <v>Enter password shorter than minimum → submit</v>
       </c>
       <c r="H16" t="str">
-        <v>HTTP 200; password updated</v>
+        <v>Password policy error shown</v>
       </c>
       <c r="I16" t="str">
-        <v>HTTP 404 — endpoint missing</v>
+        <v>Behaved as expected — assertion passed</v>
       </c>
       <c r="J16" t="str">
-        <v>Fail</v>
+        <v>PASS</v>
       </c>
       <c r="K16" t="str">
-        <v>Critical</v>
+        <v>High</v>
       </c>
       <c r="L16" t="str">
-        <v>Critical missing endpoint. Reported in Phase 2 audit.</v>
+        <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>TC-PROF-01</v>
+        <v>TC-AUTH-REGISTER-03</v>
       </c>
       <c r="B17" t="str">
-        <v>Module 2 — User Profile</v>
+        <v>M1 – Authentication</v>
       </c>
       <c r="C17" t="str">
-        <v>Route Protection</v>
+        <v>Registration</v>
       </c>
       <c r="D17" t="str">
-        <v>Functional – Security</v>
+        <v>Validation</v>
       </c>
       <c r="E17" t="str">
-        <v>/profile redirects unauthenticated guests</v>
+        <v>Terms acceptance required before submission</v>
       </c>
       <c r="F17" t="str">
-        <v>User is not logged in</v>
+        <v>On /register page</v>
       </c>
       <c r="G17" t="str">
-        <v>1. Navigate to /profile without a session</v>
+        <v>Fill form, leave terms unchecked → submit</v>
       </c>
       <c r="H17" t="str">
-        <v>Redirect to /login or 401 response</v>
+        <v>Submit blocked until terms accepted</v>
       </c>
       <c r="I17" t="str">
-        <v>Redirected correctly</v>
+        <v>Behaved as expected — assertion passed</v>
       </c>
       <c r="J17" t="str">
-        <v>Pass</v>
+        <v>PASS</v>
       </c>
       <c r="K17" t="str">
-        <v>High</v>
+        <v>Medium</v>
       </c>
       <c r="L17" t="str">
-        <v>TC-PROF-01 passing</v>
+        <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>TC-PROF-02</v>
+        <v>TC-AUTH-REGISTER-04</v>
       </c>
       <c r="B18" t="str">
-        <v>Module 2 — User Profile</v>
+        <v>M1 – Authentication</v>
       </c>
       <c r="C18" t="str">
-        <v>Profile Page Load</v>
+        <v>Registration</v>
       </c>
       <c r="D18" t="str">
-        <v>Functional – Happy Path</v>
+        <v>UI</v>
       </c>
       <c r="E18" t="str">
-        <v>Authenticated user loads profile page and sees profile card</v>
+        <v>CAPTCHA visible on registration page</v>
       </c>
       <c r="F18" t="str">
-        <v>User is logged in</v>
+        <v>On /register page</v>
       </c>
       <c r="G18" t="str">
-        <v>1. Navigate to /profile</v>
+        <v>Open /register → check CAPTCHA</v>
       </c>
       <c r="H18" t="str">
-        <v>Profile card rendered with user data</v>
+        <v>CAPTCHA challenge visible</v>
       </c>
       <c r="I18" t="str">
-        <v>Profile card displayed correctly</v>
+        <v>Behaved as expected — assertion passed</v>
       </c>
       <c r="J18" t="str">
-        <v>Pass</v>
+        <v>PASS</v>
       </c>
       <c r="K18" t="str">
-        <v>High</v>
+        <v>Medium</v>
       </c>
       <c r="L18" t="str">
         <v/>
       </c>
     </row>
-    <row r="19" xml:space="preserve">
+    <row r="19">
       <c r="A19" t="str">
-        <v>TC-PROF-03</v>
+        <v>TC-AUTH-REGISTER-05</v>
       </c>
       <c r="B19" t="str">
-        <v>Module 2 — User Profile</v>
+        <v>M1 – Authentication</v>
       </c>
       <c r="C19" t="str">
-        <v>Profile Identity</v>
+        <v>Registration</v>
       </c>
       <c r="D19" t="str">
-        <v>Functional – Happy Path</v>
+        <v>Navigation</v>
       </c>
       <c r="E19" t="str">
-        <v>Profile card shows display name, username, and social counters</v>
+        <v>Footer sign-in link navigates to /login</v>
       </c>
       <c r="F19" t="str">
-        <v>User has profile data</v>
-      </c>
-      <c r="G19" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Navigate to /profile
-2. Verify display name, @username, followers/following counts</v>
+        <v>On /register page</v>
+      </c>
+      <c r="G19" t="str">
+        <v>Click footer "Sign in" link</v>
       </c>
       <c r="H19" t="str">
-        <v>All identity fields and counters visible</v>
+        <v>Navigated to /login</v>
       </c>
       <c r="I19" t="str">
-        <v>All fields rendered</v>
+        <v>Behaved as expected — assertion passed</v>
       </c>
       <c r="J19" t="str">
-        <v>Pass</v>
+        <v>PASS</v>
       </c>
       <c r="K19" t="str">
-        <v>Medium</v>
+        <v>Low</v>
       </c>
       <c r="L19" t="str">
         <v/>
       </c>
     </row>
-    <row r="20" xml:space="preserve">
+    <row r="20">
       <c r="A20" t="str">
-        <v>TC-PROF-04</v>
+        <v>TC-AUTH-REGISTER-06</v>
       </c>
       <c r="B20" t="str">
-        <v>Module 2 — User Profile</v>
+        <v>M1 – Authentication</v>
       </c>
       <c r="C20" t="str">
-        <v>Edit Profile Modal</v>
+        <v>Registration</v>
       </c>
       <c r="D20" t="str">
-        <v>Functional – Happy Path</v>
+        <v>UI</v>
       </c>
       <c r="E20" t="str">
-        <v>Edit profile modal opens with pre-filled editable fields</v>
+        <v>Register page exposes only one login link</v>
       </c>
       <c r="F20" t="str">
-        <v>User is logged in</v>
-      </c>
-      <c r="G20" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Click Edit Profile
-2. Assert modal opens with input fields</v>
+        <v>On /register page</v>
+      </c>
+      <c r="G20" t="str">
+        <v>Count login links on /register</v>
       </c>
       <c r="H20" t="str">
-        <v>Modal visible; name, bio, location fields pre-filled</v>
+        <v>Exactly one login link</v>
       </c>
       <c r="I20" t="str">
-        <v>Modal opens with editable fields</v>
+        <v>Test failed — Register page had more than one login link in DOM</v>
       </c>
       <c r="J20" t="str">
-        <v>Pass</v>
+        <v>FAIL</v>
       </c>
       <c r="K20" t="str">
-        <v>Medium</v>
+        <v>Low</v>
       </c>
       <c r="L20" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="21" xml:space="preserve">
+        <v>Register page had more than one login link in DOM</v>
+      </c>
+    </row>
+    <row r="21">
       <c r="A21" t="str">
-        <v>TC-PROF-05</v>
+        <v>TC-AUTH-REGISTER-07</v>
       </c>
       <c r="B21" t="str">
-        <v>Module 2 — User Profile</v>
+        <v>M1 – Authentication</v>
       </c>
       <c r="C21" t="str">
-        <v>Avatar Upload</v>
+        <v>Registration</v>
       </c>
       <c r="D21" t="str">
-        <v>Functional – Happy Path</v>
+        <v>Validation</v>
       </c>
       <c r="E21" t="str">
-        <v>Avatar upload input accepts image types</v>
+        <v>Username below minimum length rejected</v>
       </c>
       <c r="F21" t="str">
-        <v>Edit modal open</v>
-      </c>
-      <c r="G21" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Open edit modal
-2. Locate avatar file input
-3. Check accept attribute</v>
+        <v>On /register page</v>
+      </c>
+      <c r="G21" t="str">
+        <v>Enter username below minimum → submit</v>
       </c>
       <c r="H21" t="str">
-        <v>Input accepts image/png, image/jpeg</v>
+        <v>Username length error shown</v>
       </c>
       <c r="I21" t="str">
-        <v>Avatar upload input accepts images</v>
+        <v>Behaved as expected — assertion passed</v>
       </c>
       <c r="J21" t="str">
-        <v>Pass</v>
+        <v>PASS</v>
       </c>
       <c r="K21" t="str">
-        <v>Medium</v>
+        <v>High</v>
       </c>
       <c r="L21" t="str">
-        <v>TC-PROF-12 (Phase 2 naming)</v>
-      </c>
-    </row>
-    <row r="22" xml:space="preserve">
+        <v/>
+      </c>
+    </row>
+    <row r="22">
       <c r="A22" t="str">
-        <v>TC-PROF-06</v>
+        <v>TC-M1-S01</v>
       </c>
       <c r="B22" t="str">
-        <v>Module 2 — User Profile</v>
+        <v>M1 – Authentication</v>
       </c>
       <c r="C22" t="str">
-        <v>Cover Upload</v>
+        <v>Social Auth</v>
       </c>
       <c r="D22" t="str">
-        <v>Functional – Happy Path</v>
+        <v>UI</v>
       </c>
       <c r="E22" t="str">
-        <v>Cover photo upload input accepts image types</v>
+        <v>Social provider button visible on login</v>
       </c>
       <c r="F22" t="str">
-        <v>Edit modal open</v>
-      </c>
-      <c r="G22" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Open edit modal
-2. Locate cover file input
-3. Check accept attribute</v>
+        <v>On /login page</v>
+      </c>
+      <c r="G22" t="str">
+        <v>Open /login → check social options</v>
       </c>
       <c r="H22" t="str">
-        <v>Input accepts image/png, image/jpeg</v>
+        <v>At least one social provider visible</v>
       </c>
       <c r="I22" t="str">
-        <v>Cover upload input accepts images</v>
+        <v>Behaved as expected — assertion passed</v>
       </c>
       <c r="J22" t="str">
-        <v>Pass</v>
+        <v>PASS</v>
       </c>
       <c r="K22" t="str">
         <v>Medium</v>
       </c>
       <c r="L22" t="str">
-        <v>TC-PROF-13 (Phase 2 naming)</v>
+        <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>TC-PROF-07</v>
+        <v>TC-M1-S02</v>
       </c>
       <c r="B23" t="str">
-        <v>Module 2 — User Profile</v>
+        <v>M1 – Authentication</v>
       </c>
       <c r="C23" t="str">
-        <v>API — Get Profile</v>
+        <v>Social Auth</v>
       </c>
       <c r="D23" t="str">
-        <v>Functional – API</v>
+        <v>UI</v>
       </c>
       <c r="E23" t="str">
-        <v>GET /api/users/me returns current user profile</v>
+        <v>Social controls are &lt;button&gt; elements</v>
       </c>
       <c r="F23" t="str">
-        <v>Valid JWT in header</v>
+        <v>On /login page</v>
       </c>
       <c r="G23" t="str">
-        <v>1. GET /api/users/me with Authorization: Bearer &lt;token&gt;</v>
+        <v>Inspect social login controls</v>
       </c>
       <c r="H23" t="str">
-        <v>HTTP 200; user object with profile fields</v>
+        <v>Controls are button elements</v>
       </c>
       <c r="I23" t="str">
-        <v>HTTP 200; profile data returned</v>
+        <v>Behaved as expected — assertion passed</v>
       </c>
       <c r="J23" t="str">
-        <v>Pass</v>
+        <v>PASS</v>
       </c>
       <c r="K23" t="str">
-        <v>High</v>
+        <v>Low</v>
       </c>
       <c r="L23" t="str">
         <v/>
@@ -1306,34 +1293,34 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>TC-PROF-08</v>
+        <v>TC-M1-S03</v>
       </c>
       <c r="B24" t="str">
-        <v>Module 2 — User Profile</v>
+        <v>M1 – Authentication</v>
       </c>
       <c r="C24" t="str">
-        <v>API — Update Profile</v>
+        <v>Social Auth</v>
       </c>
       <c r="D24" t="str">
-        <v>Functional – API</v>
+        <v>UI</v>
       </c>
       <c r="E24" t="str">
-        <v>PATCH /api/users/me updates bio field</v>
+        <v>Social options visible on register page</v>
       </c>
       <c r="F24" t="str">
-        <v>Valid JWT</v>
+        <v>On /register page</v>
       </c>
       <c r="G24" t="str">
-        <v>1. PATCH /api/users/me with { bio: "new bio" }</v>
+        <v>Open /register → check social options</v>
       </c>
       <c r="H24" t="str">
-        <v>HTTP 200; bio updated in DB</v>
+        <v>Social register options visible</v>
       </c>
       <c r="I24" t="str">
-        <v>HTTP 200; bio updated</v>
+        <v>Behaved as expected — assertion passed</v>
       </c>
       <c r="J24" t="str">
-        <v>Pass</v>
+        <v>PASS</v>
       </c>
       <c r="K24" t="str">
         <v>Medium</v>
@@ -1344,34 +1331,34 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>TC-PROF-09</v>
+        <v>TC-M1-T01</v>
       </c>
       <c r="B25" t="str">
-        <v>Module 2 — User Profile</v>
+        <v>M1 – Authentication</v>
       </c>
       <c r="C25" t="str">
-        <v>API — Delete Account</v>
+        <v>Session Tokens</v>
       </c>
       <c r="D25" t="str">
-        <v>Functional – Negative</v>
+        <v>Security</v>
       </c>
       <c r="E25" t="str">
-        <v>DELETE /api/users/me with wrong password returns 403</v>
+        <v>No tokens stored before login</v>
       </c>
       <c r="F25" t="str">
-        <v>Logged in user</v>
+        <v>Not logged in</v>
       </c>
       <c r="G25" t="str">
-        <v>1. DELETE /api/users/me with wrong password</v>
+        <v>Open app without login → check storage</v>
       </c>
       <c r="H25" t="str">
-        <v>HTTP 403 Forbidden</v>
+        <v>No JWT tokens in storage</v>
       </c>
       <c r="I25" t="str">
-        <v>HTTP 403 returned</v>
+        <v>Behaved as expected — assertion passed</v>
       </c>
       <c r="J25" t="str">
-        <v>Pass</v>
+        <v>PASS</v>
       </c>
       <c r="K25" t="str">
         <v>High</v>
@@ -1382,37 +1369,37 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>TC-PROF-10</v>
+        <v>TC-M1-T02</v>
       </c>
       <c r="B26" t="str">
-        <v>Module 2 — User Profile</v>
+        <v>M1 – Authentication</v>
       </c>
       <c r="C26" t="str">
-        <v>API — Delete Account</v>
+        <v>Session Tokens</v>
       </c>
       <c r="D26" t="str">
-        <v>Functional – Happy Path</v>
+        <v>Security</v>
       </c>
       <c r="E26" t="str">
-        <v>DELETE /api/users/me with correct credentials deletes account</v>
+        <v>Tokens stored after login</v>
       </c>
       <c r="F26" t="str">
-        <v>Logged in user</v>
+        <v>Valid credentials</v>
       </c>
       <c r="G26" t="str">
-        <v>1. DELETE /api/users/me with valid password</v>
+        <v>Log in → check localStorage</v>
       </c>
       <c r="H26" t="str">
-        <v>HTTP 200; account removed</v>
+        <v>Tokens present after login</v>
       </c>
       <c r="I26" t="str">
-        <v>HTTP 200; account deleted</v>
+        <v>Behaved as expected — assertion passed</v>
       </c>
       <c r="J26" t="str">
-        <v>Pass</v>
+        <v>PASS</v>
       </c>
       <c r="K26" t="str">
-        <v>High</v>
+        <v>Critical</v>
       </c>
       <c r="L26" t="str">
         <v/>
@@ -1420,418 +1407,414 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>TC-PROF-11</v>
+        <v>TC-M1-T03</v>
       </c>
       <c r="B27" t="str">
-        <v>Module 2 — User Profile</v>
+        <v>M1 – Authentication</v>
       </c>
       <c r="C27" t="str">
-        <v>API — Bad Request</v>
+        <v>Session Tokens</v>
       </c>
       <c r="D27" t="str">
-        <v>Functional – Negative</v>
+        <v>Security</v>
       </c>
       <c r="E27" t="str">
-        <v>PATCH /api/users/me with invalid JSON body returns 400</v>
+        <v>Token matches JWT structure (3 parts)</v>
       </c>
       <c r="F27" t="str">
-        <v>Logged in user</v>
+        <v>Logged in</v>
       </c>
       <c r="G27" t="str">
-        <v>1. PATCH /api/users/me with malformed JSON</v>
+        <v>Read access token → validate JWT format</v>
       </c>
       <c r="H27" t="str">
-        <v>HTTP 400 Bad Request</v>
+        <v>Token is a valid JWT</v>
       </c>
       <c r="I27" t="str">
-        <v>HTTP 400 returned</v>
+        <v>Behaved as expected — assertion passed</v>
       </c>
       <c r="J27" t="str">
-        <v>Pass</v>
+        <v>PASS</v>
       </c>
       <c r="K27" t="str">
+        <v>High</v>
+      </c>
+      <c r="L27" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>TC-M1-V01</v>
+      </c>
+      <c r="B28" t="str">
+        <v>M1 – Authentication</v>
+      </c>
+      <c r="C28" t="str">
+        <v>Email Verification</v>
+      </c>
+      <c r="D28" t="str">
+        <v>Functional</v>
+      </c>
+      <c r="E28" t="str">
+        <v>?verified query opens login page</v>
+      </c>
+      <c r="F28" t="str">
+        <v>Verification link used</v>
+      </c>
+      <c r="G28" t="str">
+        <v>Navigate to /login?verified=true</v>
+      </c>
+      <c r="H28" t="str">
+        <v>Login page loads</v>
+      </c>
+      <c r="I28" t="str">
+        <v>Behaved as expected — assertion passed</v>
+      </c>
+      <c r="J28" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="K28" t="str">
         <v>Medium</v>
       </c>
-      <c r="L27" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="28" xml:space="preserve">
-      <c r="A28" t="str">
-        <v>TC-PROF-12</v>
-      </c>
-      <c r="B28" t="str">
-        <v>Module 2 — User Profile</v>
-      </c>
-      <c r="C28" t="str">
-        <v>Social Links Input</v>
-      </c>
-      <c r="D28" t="str">
-        <v>Functional – UI</v>
-      </c>
-      <c r="E28" t="str">
-        <v>Edit profile form exposes at least one external link input</v>
-      </c>
-      <c r="F28" t="str">
-        <v>Edit modal open</v>
-      </c>
-      <c r="G28" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Open edit modal
-2. Check for social link / website input fields</v>
-      </c>
-      <c r="H28" t="str">
-        <v>At least one URL/link input visible</v>
-      </c>
-      <c r="I28" t="str">
-        <v>Test failed — link input not found</v>
-      </c>
-      <c r="J28" t="str">
-        <v>Fail</v>
-      </c>
-      <c r="K28" t="str">
-        <v>Low</v>
-      </c>
       <c r="L28" t="str">
-        <v>Playwright: ses-at-least-one-link-input — failed. UI may not render link field.</v>
-      </c>
-    </row>
-    <row r="29" xml:space="preserve">
+        <v/>
+      </c>
+    </row>
+    <row r="29">
       <c r="A29" t="str">
-        <v>TC-PROF-13</v>
+        <v>TC-M1-V02</v>
       </c>
       <c r="B29" t="str">
-        <v>Module 2 — User Profile</v>
+        <v>M1 – Authentication</v>
       </c>
       <c r="C29" t="str">
-        <v>Error State</v>
+        <v>Email Verification</v>
       </c>
       <c r="D29" t="str">
-        <v>Functional – Edge Case</v>
+        <v>Negative</v>
       </c>
       <c r="E29" t="str">
-        <v>Profile update failure shows a handled error state</v>
+        <v>Invalid token query still loads login</v>
       </c>
       <c r="F29" t="str">
-        <v>Simulate network/server error on save</v>
-      </c>
-      <c r="G29" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Trigger save with simulated API failure
-2. Observe UI response</v>
+        <v>On /login page</v>
+      </c>
+      <c r="G29" t="str">
+        <v>Navigate to /login?token=invalid</v>
       </c>
       <c r="H29" t="str">
-        <v>User-friendly error message displayed; no crash</v>
+        <v>Login page loads without crash</v>
       </c>
       <c r="I29" t="str">
-        <v>Error state not handled gracefully</v>
+        <v>Behaved as expected — assertion passed</v>
       </c>
       <c r="J29" t="str">
-        <v>Fail</v>
+        <v>PASS</v>
       </c>
       <c r="K29" t="str">
         <v>Medium</v>
       </c>
       <c r="L29" t="str">
-        <v>Playwright: ed-with-handled-error-state — failed</v>
+        <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>TC-SOC-01</v>
+        <v>TC-M1-V03</v>
       </c>
       <c r="B30" t="str">
-        <v>Module 3 — Social Graph</v>
+        <v>M1 – Authentication</v>
       </c>
       <c r="C30" t="str">
-        <v>Follow User</v>
+        <v>Email Verification</v>
       </c>
       <c r="D30" t="str">
-        <v>Functional – Happy Path</v>
+        <v>Negative</v>
       </c>
       <c r="E30" t="str">
-        <v>User follows another user</v>
+        <v>Missing token query still loads login</v>
       </c>
       <c r="F30" t="str">
-        <v>Both users exist; not already following</v>
+        <v>On /login page</v>
       </c>
       <c r="G30" t="str">
-        <v>1. POST /api/v1/users/:id/follow</v>
+        <v>Navigate to /login?token=</v>
       </c>
       <c r="H30" t="str">
-        <v>HTTP 200; follow relationship created</v>
+        <v>Login page loads without crash</v>
       </c>
       <c r="I30" t="str">
-        <v>HTTP 404 — route disabled</v>
+        <v>Behaved as expected — assertion passed</v>
       </c>
       <c r="J30" t="str">
-        <v>Fail</v>
+        <v>PASS</v>
       </c>
       <c r="K30" t="str">
-        <v>Critical</v>
+        <v>Low</v>
       </c>
       <c r="L30" t="str">
-        <v>social.routes.js fully commented out in current deployment</v>
+        <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>TC-SOC-02</v>
+        <v>TC-M1-V04</v>
       </c>
       <c r="B31" t="str">
-        <v>Module 3 — Social Graph</v>
+        <v>M1 – Authentication</v>
       </c>
       <c r="C31" t="str">
-        <v>Unfollow User</v>
+        <v>Email Verification</v>
       </c>
       <c r="D31" t="str">
-        <v>Functional – Happy Path</v>
+        <v>Functional</v>
       </c>
       <c r="E31" t="str">
-        <v>User unfollows a followed user</v>
+        <v>Live registration shows check-email state</v>
       </c>
       <c r="F31" t="str">
-        <v>Follow relationship exists</v>
+        <v>CAPTCHA solvable</v>
       </c>
       <c r="G31" t="str">
-        <v>1. DELETE /api/v1/users/:id/follow</v>
+        <v>Complete registration → observe result</v>
       </c>
       <c r="H31" t="str">
-        <v>HTTP 200; relationship removed</v>
+        <v>Check-email state displayed</v>
       </c>
       <c r="I31" t="str">
-        <v>HTTP 404 — route disabled</v>
+        <v>Test failed — Registration flow did not reach check-email state (CAPTCHA/network)</v>
       </c>
       <c r="J31" t="str">
-        <v>Fail</v>
+        <v>FAIL</v>
       </c>
       <c r="K31" t="str">
-        <v>Critical</v>
+        <v>High</v>
       </c>
       <c r="L31" t="str">
-        <v>Routes disabled</v>
+        <v>Registration flow did not reach check-email state (CAPTCHA/network)</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>TC-SOC-03</v>
+        <v>TC-M2-ACCESS-01</v>
       </c>
       <c r="B32" t="str">
-        <v>Module 3 — Social Graph</v>
+        <v>M2 – Profile</v>
       </c>
       <c r="C32" t="str">
-        <v>Followers List</v>
+        <v>Auth Guard</v>
       </c>
       <c r="D32" t="str">
-        <v>Functional – Happy Path</v>
+        <v>Security</v>
       </c>
       <c r="E32" t="str">
-        <v>Get list of followers for a user</v>
+        <v>Guest redirected from /profile</v>
       </c>
       <c r="F32" t="str">
-        <v>User has followers</v>
+        <v>Not logged in</v>
       </c>
       <c r="G32" t="str">
-        <v>1. GET /api/v1/users/:id/followers</v>
+        <v>Navigate to /profile without auth</v>
       </c>
       <c r="H32" t="str">
-        <v>HTTP 200; array of follower objects</v>
+        <v>Redirected to /login or gated</v>
       </c>
       <c r="I32" t="str">
-        <v>HTTP 404 — route disabled</v>
+        <v>Behaved as expected — assertion passed</v>
       </c>
       <c r="J32" t="str">
-        <v>Fail</v>
+        <v>PASS</v>
       </c>
       <c r="K32" t="str">
-        <v>High</v>
+        <v>Critical</v>
       </c>
       <c r="L32" t="str">
-        <v>Routes disabled</v>
+        <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>TC-SOC-04</v>
+        <v>TC-M2-EDIT-01</v>
       </c>
       <c r="B33" t="str">
-        <v>Module 3 — Social Graph</v>
+        <v>M2 – Profile</v>
       </c>
       <c r="C33" t="str">
-        <v>Following List</v>
+        <v>Edit Profile</v>
       </c>
       <c r="D33" t="str">
-        <v>Functional – Happy Path</v>
+        <v>Functional</v>
       </c>
       <c r="E33" t="str">
-        <v>Get list of users a user is following</v>
+        <v>Edit modal opens with editable fields</v>
       </c>
       <c r="F33" t="str">
-        <v>User is following others</v>
+        <v>Logged in, on /profile</v>
       </c>
       <c r="G33" t="str">
-        <v>1. GET /api/v1/users/:id/following</v>
+        <v>Click Edit Profile button</v>
       </c>
       <c r="H33" t="str">
-        <v>HTTP 200; array of following objects</v>
+        <v>Modal with editable fields appears</v>
       </c>
       <c r="I33" t="str">
-        <v>HTTP 404 — route disabled</v>
+        <v>Behaved as expected — assertion passed</v>
       </c>
       <c r="J33" t="str">
-        <v>Fail</v>
+        <v>PASS</v>
       </c>
       <c r="K33" t="str">
         <v>High</v>
       </c>
       <c r="L33" t="str">
-        <v>Routes disabled</v>
+        <v/>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>TC-SOC-05</v>
+        <v>TC-M2-EDIT-02</v>
       </c>
       <c r="B34" t="str">
-        <v>Module 3 — Social Graph</v>
+        <v>M2 – Profile</v>
       </c>
       <c r="C34" t="str">
-        <v>Suggested Users</v>
+        <v>Edit Profile</v>
       </c>
       <c r="D34" t="str">
-        <v>Functional – Happy Path</v>
+        <v>Functional</v>
       </c>
       <c r="E34" t="str">
-        <v>Get suggested users to follow</v>
+        <v>Avatar input accepts image MIME types</v>
       </c>
       <c r="F34" t="str">
-        <v>User is authenticated</v>
+        <v>Edit modal open</v>
       </c>
       <c r="G34" t="str">
-        <v>1. GET /api/v1/users/suggestions</v>
+        <v>Inspect avatar file input</v>
       </c>
       <c r="H34" t="str">
-        <v>HTTP 200; list of suggested users</v>
+        <v>Accepts image/* MIME types</v>
       </c>
       <c r="I34" t="str">
-        <v>HTTP 404 — route disabled</v>
+        <v>Behaved as expected — assertion passed</v>
       </c>
       <c r="J34" t="str">
-        <v>Fail</v>
+        <v>PASS</v>
       </c>
       <c r="K34" t="str">
         <v>Medium</v>
       </c>
       <c r="L34" t="str">
-        <v>Routes disabled</v>
-      </c>
-    </row>
-    <row r="35" xml:space="preserve">
+        <v/>
+      </c>
+    </row>
+    <row r="35">
       <c r="A35" t="str">
-        <v>TC-SOC-06</v>
+        <v>TC-M2-EDIT-03</v>
       </c>
       <c r="B35" t="str">
-        <v>Module 3 — Social Graph</v>
+        <v>M2 – Profile</v>
       </c>
       <c r="C35" t="str">
-        <v>Blocking</v>
+        <v>Edit Profile</v>
       </c>
       <c r="D35" t="str">
-        <v>Functional – Happy Path</v>
+        <v>Functional</v>
       </c>
       <c r="E35" t="str">
-        <v>User blocks another user</v>
+        <v>Cover photo input visible and accepts images</v>
       </c>
       <c r="F35" t="str">
-        <v>Target user exists</v>
-      </c>
-      <c r="G35" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Navigate to user profile
-2. Click Block</v>
+        <v>Edit modal open</v>
+      </c>
+      <c r="G35" t="str">
+        <v>Inspect cover file input</v>
       </c>
       <c r="H35" t="str">
-        <v>User blocked; blocked users list updated</v>
+        <v>Accepts image/* MIME types</v>
       </c>
       <c r="I35" t="str">
-        <v>Route/UI not functional</v>
+        <v>Behaved as expected — assertion passed</v>
       </c>
       <c r="J35" t="str">
-        <v>Fail</v>
+        <v>PASS</v>
       </c>
       <c r="K35" t="str">
-        <v>High</v>
+        <v>Medium</v>
       </c>
       <c r="L35" t="str">
-        <v>Routes disabled; blocked-list UI test also failed</v>
-      </c>
-    </row>
-    <row r="36" xml:space="preserve">
+        <v/>
+      </c>
+    </row>
+    <row r="36">
       <c r="A36" t="str">
-        <v>TC-SOC-07</v>
+        <v>TC-M2-EDIT-04</v>
       </c>
       <c r="B36" t="str">
-        <v>Module 3 — Social Graph</v>
+        <v>M2 – Profile</v>
       </c>
       <c r="C36" t="str">
-        <v>Social UI — Tabs</v>
+        <v>Edit Profile</v>
       </c>
       <c r="D36" t="str">
-        <v>Functional – UI</v>
+        <v>Functional</v>
       </c>
       <c r="E36" t="str">
-        <v>Social routes render tabs and route-specific headings</v>
+        <v>Cancel closes modal, keeps original name</v>
       </c>
       <c r="F36" t="str">
-        <v>User navigated to followers/following page</v>
-      </c>
-      <c r="G36" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Navigate to /&lt;user&gt;/followers
-2. Check tabs rendered</v>
+        <v>Edit modal open</v>
+      </c>
+      <c r="G36" t="str">
+        <v>Click Cancel → observe display name</v>
       </c>
       <c r="H36" t="str">
-        <v>Tabs for Followers / Following visible with headings</v>
+        <v>Modal closes, name unchanged</v>
       </c>
       <c r="I36" t="str">
-        <v>Smoke test M3-SMOKE-01 passed</v>
+        <v>Behaved as expected — assertion passed</v>
       </c>
       <c r="J36" t="str">
-        <v>Pass</v>
+        <v>PASS</v>
       </c>
       <c r="K36" t="str">
-        <v>Low</v>
+        <v>Medium</v>
       </c>
       <c r="L36" t="str">
-        <v>UI shell renders even though API is disabled</v>
+        <v/>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>TC-SOC-08</v>
+        <v>TC-M2-EDIT-05</v>
       </c>
       <c r="B37" t="str">
-        <v>Module 3 — Social Graph</v>
+        <v>M2 – Profile</v>
       </c>
       <c r="C37" t="str">
-        <v>Social UI — Empty State</v>
+        <v>Edit Profile</v>
       </c>
       <c r="D37" t="str">
-        <v>Functional – UI</v>
+        <v>Functional</v>
       </c>
       <c r="E37" t="str">
-        <v>Following page shows user content or a handled empty state</v>
+        <v>Profile URL is read-only with SoundCloud-style prefix</v>
       </c>
       <c r="F37" t="str">
-        <v>User on following page</v>
+        <v>Edit modal open</v>
       </c>
       <c r="G37" t="str">
-        <v>1. Navigate to following page without followers</v>
+        <v>Inspect profile URL field</v>
       </c>
       <c r="H37" t="str">
-        <v>Empty state message or user list shown</v>
+        <v>Field is read-only</v>
       </c>
       <c r="I37" t="str">
-        <v>M3-SMOKE-02 passed — handled state shown</v>
+        <v>Behaved as expected — assertion passed</v>
       </c>
       <c r="J37" t="str">
-        <v>Pass</v>
+        <v>PASS</v>
       </c>
       <c r="K37" t="str">
         <v>Low</v>
@@ -1840,1336 +1823,1293 @@
         <v/>
       </c>
     </row>
-    <row r="38" xml:space="preserve">
+    <row r="38">
       <c r="A38" t="str">
-        <v>TC-SOC-09</v>
+        <v>TC-M2-EDIT-06</v>
       </c>
       <c r="B38" t="str">
-        <v>Module 3 — Social Graph</v>
+        <v>M2 – Profile</v>
       </c>
       <c r="C38" t="str">
-        <v>Edit Bio in Social ctx</v>
+        <v>Edit Profile</v>
       </c>
       <c r="D38" t="str">
-        <v>Functional – UI</v>
+        <v>Functional</v>
       </c>
       <c r="E38" t="str">
-        <v>Bio text updates and cancel button works on social profile edit</v>
+        <v>Add link action exposes at least one link input</v>
       </c>
       <c r="F38" t="str">
-        <v>User on own social profile page</v>
-      </c>
-      <c r="G38" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Click edit bio
-2. Update text
-3. Click cancel</v>
+        <v>Edit modal open</v>
+      </c>
+      <c r="G38" t="str">
+        <v>Click "Add link" action</v>
       </c>
       <c r="H38" t="str">
-        <v>Text reverts on cancel; no save occurs</v>
+        <v>At least one link input appears</v>
       </c>
       <c r="I38" t="str">
-        <v>Test failed</v>
+        <v>Test failed — Add-link action did not expose a link input field</v>
       </c>
       <c r="J38" t="str">
-        <v>Fail</v>
+        <v>FAIL</v>
       </c>
       <c r="K38" t="str">
-        <v>Medium</v>
+        <v>Low</v>
       </c>
       <c r="L38" t="str">
-        <v>Playwright: rts-text-updates-and-cancel — failed</v>
+        <v>Add-link action did not expose a link input field</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>TC-SOC-10</v>
+        <v>TC-M2-EDIT-07</v>
       </c>
       <c r="B39" t="str">
-        <v>Module 3 — Social Graph</v>
+        <v>M2 – Profile</v>
       </c>
       <c r="C39" t="str">
-        <v>Blocked Users List</v>
+        <v>Edit Profile</v>
       </c>
       <c r="D39" t="str">
-        <v>Functional – UI</v>
+        <v>Validation</v>
       </c>
       <c r="E39" t="str">
-        <v>Blocked users list shows valid state</v>
+        <v>Display name required before submit</v>
       </c>
       <c r="F39" t="str">
-        <v>Some users blocked</v>
+        <v>Edit modal open</v>
       </c>
       <c r="G39" t="str">
-        <v>1. Navigate to settings &gt; blocked users</v>
+        <v>Clear display name → attempt save</v>
       </c>
       <c r="H39" t="str">
-        <v>List of blocked users or empty state</v>
+        <v>Submit blocked / error shown</v>
       </c>
       <c r="I39" t="str">
-        <v>Test failed — invalid state rendered</v>
+        <v>Behaved as expected — assertion passed</v>
       </c>
       <c r="J39" t="str">
-        <v>Fail</v>
+        <v>PASS</v>
       </c>
       <c r="K39" t="str">
-        <v>Medium</v>
+        <v>High</v>
       </c>
       <c r="L39" t="str">
-        <v>Playwright: a-valid-blocked-list-state — failed</v>
+        <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>TC-TRK-01</v>
+        <v>TC-M2-EDIT-08</v>
       </c>
       <c r="B40" t="str">
-        <v>Module 4 — Audio Tracks</v>
+        <v>M2 – Profile</v>
       </c>
       <c r="C40" t="str">
-        <v>Track Page Render</v>
+        <v>Edit Profile</v>
       </c>
       <c r="D40" t="str">
-        <v>Functional – UI</v>
+        <v>Validation</v>
       </c>
       <c r="E40" t="str">
-        <v>Track detail page renders with time format text</v>
+        <v>Bio textarea enforces 500-character limit</v>
       </c>
       <c r="F40" t="str">
-        <v>Track exists and is public</v>
+        <v>Edit modal open</v>
       </c>
       <c r="G40" t="str">
-        <v>1. Navigate to /tracks/:id</v>
+        <v>Type &gt;500 chars in bio</v>
       </c>
       <c r="H40" t="str">
-        <v>Track page loads; duration displayed in mm:ss format</v>
+        <v>Input capped at 500 characters</v>
       </c>
       <c r="I40" t="str">
-        <v>Test failed — time format text not found</v>
+        <v>Behaved as expected — assertion passed</v>
       </c>
       <c r="J40" t="str">
-        <v>Fail</v>
+        <v>PASS</v>
       </c>
       <c r="K40" t="str">
         <v>Medium</v>
       </c>
       <c r="L40" t="str">
-        <v>Playwright: nders-with-time-format-text — failed</v>
-      </c>
-    </row>
-    <row r="41" xml:space="preserve">
+        <v/>
+      </c>
+    </row>
+    <row r="41">
       <c r="A41" t="str">
-        <v>TC-TRK-02</v>
+        <v>TC-M2-CARD-01</v>
       </c>
       <c r="B41" t="str">
-        <v>Module 4 — Audio Tracks</v>
+        <v>M2 – Profile</v>
       </c>
       <c r="C41" t="str">
-        <v>Track Upload</v>
+        <v>Profile Card</v>
       </c>
       <c r="D41" t="str">
-        <v>Functional – Happy Path</v>
+        <v>UI</v>
       </c>
       <c r="E41" t="str">
-        <v>Artist uploads an MP3 track with metadata</v>
+        <v>Profile card visible for authenticated users</v>
       </c>
       <c r="F41" t="str">
-        <v>User has Artist role; upload limit not reached</v>
-      </c>
-      <c r="G41" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Go to upload page
-2. Select MP3 file
-3. Fill title, genre, tags
-4. Submit</v>
+        <v>Logged in, on /profile</v>
+      </c>
+      <c r="G41" t="str">
+        <v>Open /profile page</v>
       </c>
       <c r="H41" t="str">
-        <v>Track created with Processing state; transitions to Finished</v>
+        <v>Profile card visible</v>
       </c>
       <c r="I41" t="str">
-        <v>Not tested in e2e run</v>
+        <v>Behaved as expected — assertion passed</v>
       </c>
       <c r="J41" t="str">
-        <v>Not Tested</v>
+        <v>PASS</v>
       </c>
       <c r="K41" t="str">
         <v>High</v>
       </c>
       <c r="L41" t="str">
-        <v>Benchmark module — requires live upload flow</v>
-      </c>
-    </row>
-    <row r="42" xml:space="preserve">
+        <v/>
+      </c>
+    </row>
+    <row r="42">
       <c r="A42" t="str">
-        <v>TC-TRK-03</v>
+        <v>TC-M2-CARD-02</v>
       </c>
       <c r="B42" t="str">
-        <v>Module 4 — Audio Tracks</v>
+        <v>M2 – Profile</v>
       </c>
       <c r="C42" t="str">
-        <v>Track Privacy Toggle</v>
+        <v>Profile Card</v>
       </c>
       <c r="D42" t="str">
-        <v>Functional – Happy Path</v>
+        <v>UI</v>
       </c>
       <c r="E42" t="str">
-        <v>Artist toggles track from Public to Private</v>
+        <v>Profile identity and social counters visible</v>
       </c>
       <c r="F42" t="str">
-        <v>Track exists and is owned by user</v>
-      </c>
-      <c r="G42" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Go to track settings
-2. Toggle visibility to Private
-3. Save</v>
+        <v>Logged in, on /profile</v>
+      </c>
+      <c r="G42" t="str">
+        <v>Inspect profile card</v>
       </c>
       <c r="H42" t="str">
-        <v>Track removed from public search; accessible by direct link only</v>
+        <v>Name, avatar, follow counts visible</v>
       </c>
       <c r="I42" t="str">
-        <v>Not tested in e2e run</v>
+        <v>Behaved as expected — assertion passed</v>
       </c>
       <c r="J42" t="str">
-        <v>Not Tested</v>
+        <v>PASS</v>
       </c>
       <c r="K42" t="str">
+        <v>High</v>
+      </c>
+      <c r="L42" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>TC-M2-SAVE-01</v>
+      </c>
+      <c r="B43" t="str">
+        <v>M2 – Profile</v>
+      </c>
+      <c r="C43" t="str">
+        <v>Save Profile</v>
+      </c>
+      <c r="D43" t="str">
+        <v>Functional</v>
+      </c>
+      <c r="E43" t="str">
+        <v>Saving unchanged form yields handled success or error</v>
+      </c>
+      <c r="F43" t="str">
+        <v>Edit modal open</v>
+      </c>
+      <c r="G43" t="str">
+        <v>Open edit modal, save without changes</v>
+      </c>
+      <c r="H43" t="str">
+        <v>Success toast or handled error shown</v>
+      </c>
+      <c r="I43" t="str">
+        <v>Test failed — Saving unchanged form did not return a recognisable success/error state</v>
+      </c>
+      <c r="J43" t="str">
+        <v>FAIL</v>
+      </c>
+      <c r="K43" t="str">
         <v>Medium</v>
       </c>
-      <c r="L42" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="43" xml:space="preserve">
-      <c r="A43" t="str">
-        <v>TC-TRK-04</v>
-      </c>
-      <c r="B43" t="str">
-        <v>Module 4 — Audio Tracks</v>
-      </c>
-      <c r="C43" t="str">
-        <v>Waveform Display</v>
-      </c>
-      <c r="D43" t="str">
-        <v>Functional – UI</v>
-      </c>
-      <c r="E43" t="str">
-        <v>Track page renders waveform visualization</v>
-      </c>
-      <c r="F43" t="str">
-        <v>Track page loaded</v>
-      </c>
-      <c r="G43" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Navigate to a track page
-2. Inspect waveform element</v>
-      </c>
-      <c r="H43" t="str">
-        <v>Waveform SVG/canvas element visible</v>
-      </c>
-      <c r="I43" t="str">
-        <v>Not tested in e2e run</v>
-      </c>
-      <c r="J43" t="str">
-        <v>Not Tested</v>
-      </c>
-      <c r="K43" t="str">
-        <v>Low</v>
-      </c>
       <c r="L43" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="44" xml:space="preserve">
+        <v>Saving unchanged form did not return a recognisable success/error state</v>
+      </c>
+    </row>
+    <row r="44">
       <c r="A44" t="str">
-        <v>TC-PLAY-01</v>
+        <v>TC-M2-SAVE-02</v>
       </c>
       <c r="B44" t="str">
-        <v>Module 5 — Playback</v>
+        <v>M2 – Profile</v>
       </c>
       <c r="C44" t="str">
-        <v>Play Button</v>
+        <v>Save Profile</v>
       </c>
       <c r="D44" t="str">
-        <v>Functional – Happy Path</v>
+        <v>Functional</v>
       </c>
       <c r="E44" t="str">
-        <v>Play button is visible on track hero and triggers playback</v>
+        <v>Display name and bio update persists or shows error</v>
       </c>
       <c r="F44" t="str">
-        <v>Public track page loaded</v>
-      </c>
-      <c r="G44" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Navigate to /tracks/:id
-2. Assert play button exists
-3. Click play</v>
+        <v>Edit modal open</v>
+      </c>
+      <c r="G44" t="str">
+        <v>Update display name and bio → save</v>
       </c>
       <c r="H44" t="str">
-        <v>Play button visible; audio begins on click</v>
+        <v>Changes reflected or handled error</v>
       </c>
       <c r="I44" t="str">
-        <v>Test failed — play button not found on hero</v>
+        <v>Test failed — Display-name/bio save did not reflect change or show handled error</v>
       </c>
       <c r="J44" t="str">
-        <v>Fail</v>
+        <v>FAIL</v>
       </c>
       <c r="K44" t="str">
-        <v>Critical</v>
+        <v>High</v>
       </c>
       <c r="L44" t="str">
-        <v>Playwright: on-is-visible-on-track-hero — failed</v>
-      </c>
-    </row>
-    <row r="45" xml:space="preserve">
+        <v>Display-name/bio save did not reflect change or show handled error</v>
+      </c>
+    </row>
+    <row r="45">
       <c r="A45" t="str">
-        <v>TC-PLAY-02</v>
+        <v>TC-M2-SAVE-03</v>
       </c>
       <c r="B45" t="str">
-        <v>Module 5 — Playback</v>
+        <v>M2 – Profile</v>
       </c>
       <c r="C45" t="str">
-        <v>Playing State UI</v>
+        <v>Save Profile</v>
       </c>
       <c r="D45" t="str">
-        <v>Functional – UI</v>
+        <v>Functional</v>
       </c>
       <c r="E45" t="str">
-        <v>Clicking play transitions hero to is-playing state</v>
+        <v>City and country update persists or shows error</v>
       </c>
       <c r="F45" t="str">
-        <v>Track page loaded</v>
-      </c>
-      <c r="G45" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Click play
-2. Check playing CSS class or aria state</v>
+        <v>Edit modal open</v>
+      </c>
+      <c r="G45" t="str">
+        <v>Update city/country → save</v>
       </c>
       <c r="H45" t="str">
-        <v>Hero shows playing indicator (e.g. pause icon, progress bar active)</v>
+        <v>Changes reflected or handled error</v>
       </c>
       <c r="I45" t="str">
-        <v>Test failed — playing state not reflected</v>
+        <v>Test failed — City/country save did not persist or show handled error</v>
       </c>
       <c r="J45" t="str">
-        <v>Fail</v>
+        <v>FAIL</v>
       </c>
       <c r="K45" t="str">
-        <v>High</v>
+        <v>Medium</v>
       </c>
       <c r="L45" t="str">
-        <v>Playwright: es-hero-to-is-playing-state — failed</v>
-      </c>
-    </row>
-    <row r="46" xml:space="preserve">
+        <v>City/country save did not persist or show handled error</v>
+      </c>
+    </row>
+    <row r="46">
       <c r="A46" t="str">
-        <v>TC-PLAY-03</v>
+        <v>TC-M2-SAVE-04</v>
       </c>
       <c r="B46" t="str">
-        <v>Module 5 — Playback</v>
+        <v>M2 – Profile</v>
       </c>
       <c r="C46" t="str">
-        <v>Progress Bar</v>
+        <v>Save Profile</v>
       </c>
       <c r="D46" t="str">
-        <v>Functional – UI</v>
+        <v>Validation</v>
       </c>
       <c r="E46" t="str">
-        <v>Progress bar is present on the page during playback</v>
+        <v>Too-long display name rejected with error</v>
       </c>
       <c r="F46" t="str">
-        <v>Track playing</v>
-      </c>
-      <c r="G46" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Start playback
-2. Assert progress bar element exists</v>
+        <v>Edit modal open</v>
+      </c>
+      <c r="G46" t="str">
+        <v>Enter 300-char display name → save</v>
       </c>
       <c r="H46" t="str">
-        <v>Progress bar element visible and updating</v>
+        <v>Validation error shown</v>
       </c>
       <c r="I46" t="str">
-        <v>Test failed</v>
+        <v>Test failed — Overly long display name was not rejected with a visible error</v>
       </c>
       <c r="J46" t="str">
-        <v>Fail</v>
+        <v>FAIL</v>
       </c>
       <c r="K46" t="str">
-        <v>High</v>
+        <v>Medium</v>
       </c>
       <c r="L46" t="str">
-        <v>Playwright: bar-is-present-on-the-page — failed</v>
-      </c>
-    </row>
-    <row r="47" xml:space="preserve">
+        <v>Overly long display name was not rejected with a visible error</v>
+      </c>
+    </row>
+    <row r="47">
       <c r="A47" t="str">
-        <v>TC-PLAY-04</v>
+        <v>TC-M3-MOD-01</v>
       </c>
       <c r="B47" t="str">
-        <v>Module 5 — Playback</v>
+        <v>M3 – Social</v>
       </c>
       <c r="C47" t="str">
-        <v>Seek</v>
+        <v>Block User</v>
       </c>
       <c r="D47" t="str">
-        <v>Functional – Happy Path</v>
+        <v>Functional</v>
       </c>
       <c r="E47" t="str">
-        <v>Progress bar is interactive for seeking</v>
+        <v>Block modal opens from card and closes on cancel</v>
       </c>
       <c r="F47" t="str">
-        <v>Track playing</v>
-      </c>
-      <c r="G47" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Click on progress bar at 50%
-2. Observe playback position</v>
+        <v>Logged in, on social page</v>
+      </c>
+      <c r="G47" t="str">
+        <v>Open card actions → Block → cancel</v>
       </c>
       <c r="H47" t="str">
-        <v>Playback jumps to clicked position</v>
+        <v>Modal opens, cancel closes it</v>
       </c>
       <c r="I47" t="str">
-        <v>Test failed</v>
+        <v>Behaved as expected — assertion passed</v>
       </c>
       <c r="J47" t="str">
-        <v>Fail</v>
+        <v>PASS</v>
       </c>
       <c r="K47" t="str">
         <v>High</v>
       </c>
       <c r="L47" t="str">
-        <v>Playwright: and-interactive-for-seeking — failed</v>
-      </c>
-    </row>
-    <row r="48" xml:space="preserve">
+        <v/>
+      </c>
+    </row>
+    <row r="48">
       <c r="A48" t="str">
-        <v>TC-PLAY-05</v>
+        <v>TC-M3-MOD-02</v>
       </c>
       <c r="B48" t="str">
-        <v>Module 5 — Playback</v>
+        <v>M3 – Social</v>
       </c>
       <c r="C48" t="str">
-        <v>Playback States</v>
+        <v>Block User</v>
       </c>
       <c r="D48" t="str">
-        <v>Functional – Edge Case</v>
+        <v>Functional</v>
       </c>
       <c r="E48" t="str">
-        <v>Player handles Playable, Preview, and Blocked access tiers without crashing</v>
+        <v>Blocked users route shows list or handled state</v>
       </c>
       <c r="F48" t="str">
-        <v>Different user tier accounts</v>
-      </c>
-      <c r="G48" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Test playback as Free user
-2. Test playback as Pro user
-3. Test blocked region</v>
+        <v>Logged in</v>
+      </c>
+      <c r="G48" t="str">
+        <v>Navigate to blocked tab</v>
       </c>
       <c r="H48" t="str">
-        <v>Correct state per tier; no JS crash</v>
+        <v>List or empty state shown</v>
       </c>
       <c r="I48" t="str">
-        <v>Test failed — tier handling crashed or showed wrong state</v>
+        <v>Test failed — Blocked-users route showed neither list content nor a handled empty state</v>
       </c>
       <c r="J48" t="str">
-        <v>Fail</v>
+        <v>FAIL</v>
       </c>
       <c r="K48" t="str">
         <v>High</v>
       </c>
       <c r="L48" t="str">
-        <v>Playwright: s-Playable-Preview-Blocked — failed</v>
+        <v>Blocked-users route showed neither list content nor a handled empty state</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>TC-PLAY-06</v>
+        <v>TC-M3-MOD-03</v>
       </c>
       <c r="B49" t="str">
-        <v>Module 5 — Playback</v>
+        <v>M3 – Social</v>
       </c>
       <c r="C49" t="str">
-        <v>Listening History</v>
+        <v>Block User</v>
       </c>
       <c r="D49" t="str">
-        <v>Functional – Happy Path</v>
+        <v>Functional</v>
       </c>
       <c r="E49" t="str">
-        <v>Profile shows playback history section</v>
+        <v>Edit reason modal accepts text and cancel works</v>
       </c>
       <c r="F49" t="str">
-        <v>User has listened to tracks</v>
+        <v>Block reason modal open</v>
       </c>
       <c r="G49" t="str">
-        <v>1. Navigate to /profile/history or history tab</v>
+        <v>Edit reason text → cancel</v>
       </c>
       <c r="H49" t="str">
-        <v>List of recently played tracks shown</v>
+        <v>Modal closes without saving</v>
       </c>
       <c r="I49" t="str">
-        <v>Test failed — history section not found</v>
+        <v>Test failed — Edit-reason modal did not accept text updates or cancel correctly</v>
       </c>
       <c r="J49" t="str">
-        <v>Fail</v>
+        <v>FAIL</v>
       </c>
       <c r="K49" t="str">
         <v>Medium</v>
       </c>
       <c r="L49" t="str">
-        <v>Playwright: rs-playback-history-section — failed</v>
+        <v>Edit-reason modal did not accept text updates or cancel correctly</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>TC-PLAY-07</v>
+        <v>TC-M3-MOD-04</v>
       </c>
       <c r="B50" t="str">
-        <v>Module 5 — Playback</v>
+        <v>M3 – Social</v>
       </c>
       <c r="C50" t="str">
-        <v>Recently Played</v>
+        <v>Block User</v>
       </c>
       <c r="D50" t="str">
-        <v>Functional – Happy Path</v>
+        <v>Functional</v>
       </c>
       <c r="E50" t="str">
-        <v>Recently played shows cards or empty state</v>
+        <v>Unblock results in valid blocked-list state</v>
       </c>
       <c r="F50" t="str">
-        <v>User authenticated</v>
+        <v>User is blocked</v>
       </c>
       <c r="G50" t="str">
-        <v>1. Navigate to recently played section</v>
+        <v>Unblock the user</v>
       </c>
       <c r="H50" t="str">
-        <v>Track cards or "Nothing played yet" message</v>
+        <v>User removed from blocked list</v>
       </c>
       <c r="I50" t="str">
-        <v>Test failed</v>
+        <v>Test failed — Unblock action did not result in a valid blocked-list state</v>
       </c>
       <c r="J50" t="str">
-        <v>Fail</v>
+        <v>FAIL</v>
       </c>
       <c r="K50" t="str">
-        <v>Medium</v>
+        <v>High</v>
       </c>
       <c r="L50" t="str">
-        <v>Playwright: shows-cards-or-empty-state — failed</v>
-      </c>
-    </row>
-    <row r="51" xml:space="preserve">
+        <v>Unblock action did not result in a valid blocked-list state</v>
+      </c>
+    </row>
+    <row r="51">
       <c r="A51" t="str">
-        <v>TC-PLAY-08</v>
+        <v>TC-M3-NAV-01</v>
       </c>
       <c r="B51" t="str">
-        <v>Module 5 — Playback</v>
+        <v>M3 – Social</v>
       </c>
       <c r="C51" t="str">
-        <v>History on Navigate Away</v>
+        <v>Navigation</v>
       </c>
       <c r="D51" t="str">
-        <v>Functional – Happy Path</v>
+        <v>Navigation</v>
       </c>
       <c r="E51" t="str">
-        <v>Navigating away from track page preserves history entry</v>
+        <v>Social tabs navigate to following/followers/blocked</v>
       </c>
       <c r="F51" t="str">
-        <v>Track played partially</v>
-      </c>
-      <c r="G51" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Play track
-2. Navigate to another page
-3. Check history</v>
+        <v>Logged in</v>
+      </c>
+      <c r="G51" t="str">
+        <v>Click each social tab</v>
       </c>
       <c r="H51" t="str">
-        <v>Track appears in history</v>
+        <v>Correct route loaded per tab</v>
       </c>
       <c r="I51" t="str">
-        <v>Test failed</v>
+        <v>Test failed — Social tabs did not correctly navigate to following/followers/blocked routes</v>
       </c>
       <c r="J51" t="str">
-        <v>Fail</v>
+        <v>FAIL</v>
       </c>
       <c r="K51" t="str">
         <v>Medium</v>
       </c>
       <c r="L51" t="str">
-        <v>Playwright: gating-away-from-track-page — failed</v>
+        <v>Social tabs did not correctly navigate to following/followers/blocked routes</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>TC-PLAY-09</v>
+        <v>TC-M3-NET-01</v>
       </c>
       <c r="B52" t="str">
-        <v>Module 5 — Playback</v>
+        <v>M3 – Social</v>
       </c>
       <c r="C52" t="str">
-        <v>History Page Visible</v>
+        <v>Network</v>
       </c>
       <c r="D52" t="str">
-        <v>Functional – UI</v>
+        <v>Functional</v>
       </c>
       <c r="E52" t="str">
-        <v>History page is accessible and visible</v>
+        <v>Following view shows cards or handled state</v>
       </c>
       <c r="F52" t="str">
-        <v>User authenticated</v>
+        <v>Logged in</v>
       </c>
       <c r="G52" t="str">
-        <v>1. Navigate to history page URL</v>
+        <v>Open following tab</v>
       </c>
       <c r="H52" t="str">
-        <v>History page renders</v>
+        <v>User cards or empty state</v>
       </c>
       <c r="I52" t="str">
-        <v>Test failed</v>
+        <v>Behaved as expected — assertion passed</v>
       </c>
       <c r="J52" t="str">
-        <v>Fail</v>
+        <v>PASS</v>
       </c>
       <c r="K52" t="str">
+        <v>High</v>
+      </c>
+      <c r="L52" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>TC-M3-NET-02</v>
+      </c>
+      <c r="B53" t="str">
+        <v>M3 – Social</v>
+      </c>
+      <c r="C53" t="str">
+        <v>Network</v>
+      </c>
+      <c r="D53" t="str">
+        <v>Functional</v>
+      </c>
+      <c r="E53" t="str">
+        <v>Followers view shows cards or handled state</v>
+      </c>
+      <c r="F53" t="str">
+        <v>Logged in</v>
+      </c>
+      <c r="G53" t="str">
+        <v>Open followers tab</v>
+      </c>
+      <c r="H53" t="str">
+        <v>User cards or empty state</v>
+      </c>
+      <c r="I53" t="str">
+        <v>Behaved as expected — assertion passed</v>
+      </c>
+      <c r="J53" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="K53" t="str">
+        <v>High</v>
+      </c>
+      <c r="L53" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>TC-M3-NET-03</v>
+      </c>
+      <c r="B54" t="str">
+        <v>M3 – Social</v>
+      </c>
+      <c r="C54" t="str">
+        <v>Network</v>
+      </c>
+      <c r="D54" t="str">
+        <v>UI</v>
+      </c>
+      <c r="E54" t="str">
+        <v>Suggested users panel rendered or absent</v>
+      </c>
+      <c r="F54" t="str">
+        <v>Logged in</v>
+      </c>
+      <c r="G54" t="str">
+        <v>Check suggested panel</v>
+      </c>
+      <c r="H54" t="str">
+        <v>Present or intentionally absent</v>
+      </c>
+      <c r="I54" t="str">
+        <v>Behaved as expected — assertion passed</v>
+      </c>
+      <c r="J54" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="K54" t="str">
+        <v>Low</v>
+      </c>
+      <c r="L54" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>TC-M3-NET-04</v>
+      </c>
+      <c r="B55" t="str">
+        <v>M3 – Social</v>
+      </c>
+      <c r="C55" t="str">
+        <v>Network</v>
+      </c>
+      <c r="D55" t="str">
+        <v>Negative</v>
+      </c>
+      <c r="E55" t="str">
+        <v>Impossible filter shows no-match state</v>
+      </c>
+      <c r="F55" t="str">
+        <v>Logged in</v>
+      </c>
+      <c r="G55" t="str">
+        <v>Search "xyzxyzxyz123"</v>
+      </c>
+      <c r="H55" t="str">
+        <v>No results / empty state</v>
+      </c>
+      <c r="I55" t="str">
+        <v>Behaved as expected — assertion passed</v>
+      </c>
+      <c r="J55" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="K55" t="str">
         <v>Medium</v>
       </c>
-      <c r="L52" t="str">
-        <v>Playwright: is-visible-on-history-page — failed</v>
-      </c>
-    </row>
-    <row r="53" xml:space="preserve">
-      <c r="A53" t="str">
-        <v>TC-ENG-01</v>
-      </c>
-      <c r="B53" t="str">
-        <v>Module 6 — Engagement</v>
-      </c>
-      <c r="C53" t="str">
-        <v>Like Button</v>
-      </c>
-      <c r="D53" t="str">
-        <v>Functional – Happy Path</v>
-      </c>
-      <c r="E53" t="str">
-        <v>Like button is visible and clickable on track actions row</v>
-      </c>
-      <c r="F53" t="str">
-        <v>Track page loaded; user authenticated</v>
-      </c>
-      <c r="G53" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Navigate to track page
-2. Assert like button
-3. Click like</v>
-      </c>
-      <c r="H53" t="str">
-        <v>Like button present and clickable; like count increments</v>
-      </c>
-      <c r="I53" t="str">
-        <v>Test failed — like button not found</v>
-      </c>
-      <c r="J53" t="str">
-        <v>Fail</v>
-      </c>
-      <c r="K53" t="str">
-        <v>High</v>
-      </c>
-      <c r="L53" t="str">
-        <v>Playwright: isible-in-track-actions-row + on-is-present-and-clickable — failed (x2)</v>
-      </c>
-    </row>
-    <row r="54" xml:space="preserve">
-      <c r="A54" t="str">
-        <v>TC-ENG-02</v>
-      </c>
-      <c r="B54" t="str">
-        <v>Module 6 — Engagement</v>
-      </c>
-      <c r="C54" t="str">
-        <v>Repost Button</v>
-      </c>
-      <c r="D54" t="str">
-        <v>Functional – Happy Path</v>
-      </c>
-      <c r="E54" t="str">
-        <v>Repost button is visible and clickable on track actions row</v>
-      </c>
-      <c r="F54" t="str">
-        <v>Track page loaded; user authenticated</v>
-      </c>
-      <c r="G54" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Navigate to track page
-2. Assert repost button
-3. Click repost</v>
-      </c>
-      <c r="H54" t="str">
-        <v>Repost button present; repost count increments</v>
-      </c>
-      <c r="I54" t="str">
-        <v>Test failed</v>
-      </c>
-      <c r="J54" t="str">
-        <v>Fail</v>
-      </c>
-      <c r="K54" t="str">
-        <v>High</v>
-      </c>
-      <c r="L54" t="str">
-        <v>Playwright: isible-in-track-actions-row + on-is-present-and-clickable — failed (x2)</v>
-      </c>
-    </row>
-    <row r="55" xml:space="preserve">
-      <c r="A55" t="str">
-        <v>TC-ENG-03</v>
-      </c>
-      <c r="B55" t="str">
-        <v>Module 6 — Engagement</v>
-      </c>
-      <c r="C55" t="str">
-        <v>Comment Bar</v>
-      </c>
-      <c r="D55" t="str">
-        <v>Functional – UI</v>
-      </c>
-      <c r="E55" t="str">
-        <v>Comment bar is visible on track page</v>
-      </c>
-      <c r="F55" t="str">
-        <v>Track page loaded</v>
-      </c>
-      <c r="G55" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Navigate to track page
-2. Scroll to comments section</v>
-      </c>
-      <c r="H55" t="str">
-        <v>Comment input bar/section visible</v>
-      </c>
-      <c r="I55" t="str">
-        <v>Test failed</v>
-      </c>
-      <c r="J55" t="str">
-        <v>Fail</v>
-      </c>
-      <c r="K55" t="str">
-        <v>High</v>
-      </c>
       <c r="L55" t="str">
-        <v>Playwright: ar-is-visible-on-track-page — failed</v>
-      </c>
-    </row>
-    <row r="56" xml:space="preserve">
+        <v/>
+      </c>
+    </row>
+    <row r="56">
       <c r="A56" t="str">
-        <v>TC-ENG-04</v>
+        <v>TC-M3-NET-05</v>
       </c>
       <c r="B56" t="str">
-        <v>Module 6 — Engagement</v>
+        <v>M3 – Social</v>
       </c>
       <c r="C56" t="str">
-        <v>Comment Composer</v>
+        <v>Pagination</v>
       </c>
       <c r="D56" t="str">
-        <v>Functional – UI</v>
+        <v>Functional</v>
       </c>
       <c r="E56" t="str">
-        <v>Comment composer input is visible</v>
+        <v>Pagination controls valid when shown</v>
       </c>
       <c r="F56" t="str">
-        <v>Track page loaded; user authenticated</v>
-      </c>
-      <c r="G56" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Navigate to track page
-2. Assert comment input field</v>
+        <v>Many users</v>
+      </c>
+      <c r="G56" t="str">
+        <v>Check pagination UI</v>
       </c>
       <c r="H56" t="str">
-        <v>Text input for composing comment visible</v>
+        <v>Valid next/prev controls</v>
       </c>
       <c r="I56" t="str">
-        <v>Test failed</v>
+        <v>Behaved as expected — assertion passed</v>
       </c>
       <c r="J56" t="str">
-        <v>Fail</v>
+        <v>PASS</v>
       </c>
       <c r="K56" t="str">
         <v>Medium</v>
       </c>
       <c r="L56" t="str">
-        <v>Playwright: visible-in-comment-composer — failed</v>
-      </c>
-    </row>
-    <row r="57" xml:space="preserve">
+        <v/>
+      </c>
+    </row>
+    <row r="57">
       <c r="A57" t="str">
-        <v>TC-ENG-05</v>
+        <v>TC-M3-REL-01</v>
       </c>
       <c r="B57" t="str">
-        <v>Module 6 — Engagement</v>
+        <v>M3 – Social</v>
       </c>
       <c r="C57" t="str">
-        <v>Comment Thread</v>
+        <v>Follow</v>
       </c>
       <c r="D57" t="str">
-        <v>Functional – Happy Path</v>
+        <v>Functional</v>
       </c>
       <c r="E57" t="str">
-        <v>Comment section renders thread or empty state</v>
+        <v>Follow controls on follower cards or handled state</v>
       </c>
       <c r="F57" t="str">
-        <v>Track page loaded</v>
-      </c>
-      <c r="G57" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Navigate to track page comments
-2. Check for thread or empty message</v>
+        <v>Logged in</v>
+      </c>
+      <c r="G57" t="str">
+        <v>View follower cards → check follow button</v>
       </c>
       <c r="H57" t="str">
-        <v>Comment thread or "No comments yet" message shown</v>
+        <v>Follow button present or handled</v>
       </c>
       <c r="I57" t="str">
-        <v>Test failed</v>
+        <v>Behaved as expected — assertion passed</v>
       </c>
       <c r="J57" t="str">
-        <v>Fail</v>
+        <v>PASS</v>
       </c>
       <c r="K57" t="str">
-        <v>Medium</v>
+        <v>High</v>
       </c>
       <c r="L57" t="str">
-        <v>Playwright: with-thread-or-empty-state — failed</v>
-      </c>
-    </row>
-    <row r="58" xml:space="preserve">
+        <v/>
+      </c>
+    </row>
+    <row r="58">
       <c r="A58" t="str">
-        <v>TC-ENG-06</v>
+        <v>TC-M3-REL-02</v>
       </c>
       <c r="B58" t="str">
-        <v>Module 6 — Engagement</v>
+        <v>M3 – Social</v>
       </c>
       <c r="C58" t="str">
-        <v>Likers List Panel</v>
+        <v>Follow</v>
       </c>
       <c r="D58" t="str">
-        <v>Functional – UI</v>
+        <v>Functional</v>
       </c>
       <c r="E58" t="str">
-        <v>Likers section list panel renders</v>
+        <v>Follow toggle leaves control in valid state</v>
       </c>
       <c r="F58" t="str">
-        <v>Track has likes</v>
-      </c>
-      <c r="G58" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Click "N likes" on a track
-2. Check modal/panel</v>
+        <v>Logged in</v>
+      </c>
+      <c r="G58" t="str">
+        <v>Click follow → observe state</v>
       </c>
       <c r="H58" t="str">
-        <v>List of users who liked the track shown</v>
+        <v>Button reflects new state</v>
       </c>
       <c r="I58" t="str">
-        <v>Test failed</v>
+        <v>Behaved as expected — assertion passed</v>
       </c>
       <c r="J58" t="str">
-        <v>Fail</v>
+        <v>PASS</v>
       </c>
       <c r="K58" t="str">
-        <v>Low</v>
+        <v>High</v>
       </c>
       <c r="L58" t="str">
-        <v>Playwright: renders-section-list-panel — failed (x2)</v>
-      </c>
-    </row>
-    <row r="59" xml:space="preserve">
+        <v/>
+      </c>
+    </row>
+    <row r="59">
       <c r="A59" t="str">
-        <v>TC-PL-01</v>
+        <v>TC-M4-META-01</v>
       </c>
       <c r="B59" t="str">
-        <v>Module 7 — Playlists</v>
+        <v>M4 – Tracks</v>
       </c>
       <c r="C59" t="str">
-        <v>Playlist Page with Tracks</v>
+        <v>Track Metadata</v>
       </c>
       <c r="D59" t="str">
-        <v>Functional – UI</v>
+        <v>UI</v>
       </c>
       <c r="E59" t="str">
-        <v>Playlist detail page renders with track list</v>
+        <v>Track hero title visible on track page</v>
       </c>
       <c r="F59" t="str">
-        <v>Playlist exists with tracks</v>
-      </c>
-      <c r="G59" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Navigate to /sets/:id
-2. Check track list renders</v>
+        <v>On a track page</v>
+      </c>
+      <c r="G59" t="str">
+        <v>Open /tracks/:id</v>
       </c>
       <c r="H59" t="str">
-        <v>Track list displayed inside playlist</v>
+        <v>Track title in hero</v>
       </c>
       <c r="I59" t="str">
-        <v>Test failed</v>
+        <v>Behaved as expected — assertion passed</v>
       </c>
       <c r="J59" t="str">
-        <v>Fail</v>
+        <v>PASS</v>
       </c>
       <c r="K59" t="str">
         <v>High</v>
       </c>
       <c r="L59" t="str">
-        <v>Playwright: cks-renders-with-track-list — failed</v>
-      </c>
-    </row>
-    <row r="60" xml:space="preserve">
+        <v/>
+      </c>
+    </row>
+    <row r="60">
       <c r="A60" t="str">
-        <v>TC-PL-02</v>
+        <v>TC-M4-META-02</v>
       </c>
       <c r="B60" t="str">
-        <v>Module 7 — Playlists</v>
+        <v>M4 – Tracks</v>
       </c>
       <c r="C60" t="str">
-        <v>Create Playlist Option</v>
+        <v>Track Metadata</v>
       </c>
       <c r="D60" t="str">
-        <v>Functional – UI</v>
+        <v>UI</v>
       </c>
       <c r="E60" t="str">
-        <v>Library view shows playlists or a Create Playlist option</v>
+        <v>Artist chip link renders on hero</v>
       </c>
       <c r="F60" t="str">
-        <v>User authenticated</v>
-      </c>
-      <c r="G60" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Navigate to /library or /sets
-2. Check for playlist list or create button</v>
+        <v>On a track page</v>
+      </c>
+      <c r="G60" t="str">
+        <v>Inspect track hero</v>
       </c>
       <c r="H60" t="str">
-        <v>Playlist list or "Create playlist" CTA visible</v>
+        <v>Artist chip/link present</v>
       </c>
       <c r="I60" t="str">
-        <v>Test failed</v>
+        <v>Behaved as expected — assertion passed</v>
       </c>
       <c r="J60" t="str">
-        <v>Fail</v>
+        <v>PASS</v>
       </c>
       <c r="K60" t="str">
-        <v>Medium</v>
+        <v>High</v>
       </c>
       <c r="L60" t="str">
-        <v>Playwright: s-or-Create-playlist-option — failed (x2)</v>
-      </c>
-    </row>
-    <row r="61" xml:space="preserve">
+        <v/>
+      </c>
+    </row>
+    <row r="61">
       <c r="A61" t="str">
-        <v>TC-PL-03</v>
+        <v>TC-M4-META-03</v>
       </c>
       <c r="B61" t="str">
-        <v>Module 7 — Playlists</v>
+        <v>M4 – Tracks</v>
       </c>
       <c r="C61" t="str">
-        <v>Create Playlist Form</v>
+        <v>Track Metadata</v>
       </c>
       <c r="D61" t="str">
-        <v>Functional – UI</v>
+        <v>UI</v>
       </c>
       <c r="E61" t="str">
-        <v>Create playlist form shows title input and privacy options</v>
+        <v>Genre pill renders on track hero</v>
       </c>
       <c r="F61" t="str">
-        <v>Create playlist modal open</v>
-      </c>
-      <c r="G61" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Click Create Playlist
-2. Check form fields</v>
+        <v>On a track page</v>
+      </c>
+      <c r="G61" t="str">
+        <v>Inspect hero for genre pill</v>
       </c>
       <c r="H61" t="str">
-        <v>Title input + Public/Private toggle visible</v>
+        <v>Genre/type pill visible</v>
       </c>
       <c r="I61" t="str">
-        <v>Test failed</v>
+        <v>Behaved as expected — assertion passed</v>
       </c>
       <c r="J61" t="str">
-        <v>Fail</v>
+        <v>PASS</v>
       </c>
       <c r="K61" t="str">
         <v>Medium</v>
       </c>
       <c r="L61" t="str">
-        <v>Playwright: e-input-and-privacy-options — failed</v>
-      </c>
-    </row>
-    <row r="62" xml:space="preserve">
+        <v/>
+      </c>
+    </row>
+    <row r="62">
       <c r="A62" t="str">
-        <v>TC-PL-04</v>
+        <v>TC-M4-TRN-01</v>
       </c>
       <c r="B62" t="str">
-        <v>Module 7 — Playlists</v>
+        <v>M4 – Tracks</v>
       </c>
       <c r="C62" t="str">
-        <v>Create Playlist Success</v>
+        <v>Track Page</v>
       </c>
       <c r="D62" t="str">
-        <v>Functional – Happy Path</v>
+        <v>Functional</v>
       </c>
       <c r="E62" t="str">
-        <v>Creating a playlist shows success confirmation</v>
+        <v>Track page loads or shows unavailable — not blank</v>
       </c>
       <c r="F62" t="str">
-        <v>Form filled with valid title</v>
-      </c>
-      <c r="G62" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Fill title
-2. Set visibility
-3. Submit</v>
+        <v>Track ID exists</v>
+      </c>
+      <c r="G62" t="str">
+        <v>Navigate to /tracks/:id</v>
       </c>
       <c r="H62" t="str">
-        <v>Success toast/modal confirms playlist created</v>
+        <v>Content or "unavailable" — not blank</v>
       </c>
       <c r="I62" t="str">
-        <v>Test failed</v>
+        <v>Behaved as expected — assertion passed</v>
       </c>
       <c r="J62" t="str">
-        <v>Fail</v>
+        <v>PASS</v>
       </c>
       <c r="K62" t="str">
-        <v>High</v>
+        <v>Critical</v>
       </c>
       <c r="L62" t="str">
-        <v>Playwright: shows-success-confirmation — failed</v>
-      </c>
-    </row>
-    <row r="63" xml:space="preserve">
+        <v/>
+      </c>
+    </row>
+    <row r="63">
       <c r="A63" t="str">
-        <v>TC-SRCH-01</v>
+        <v>TC-M4-TRN-02</v>
       </c>
       <c r="B63" t="str">
-        <v>Module 8 — Search &amp; Discovery</v>
+        <v>M4 – Tracks</v>
       </c>
       <c r="C63" t="str">
-        <v>Global Search</v>
+        <v>Track Page</v>
       </c>
       <c r="D63" t="str">
-        <v>Functional – Happy Path</v>
+        <v>Robustness</v>
       </c>
       <c r="E63" t="str">
-        <v>Search bar returns relevant tracks and users for a keyword</v>
+        <v>Track page never shows blank screen</v>
       </c>
       <c r="F63" t="str">
-        <v>Tracks and users exist in DB</v>
-      </c>
-      <c r="G63" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Enter keyword in search bar
-2. Submit
-3. Inspect results</v>
+        <v>Track ID exists</v>
+      </c>
+      <c r="G63" t="str">
+        <v>Navigate to /tracks/:id</v>
       </c>
       <c r="H63" t="str">
-        <v>Matching tracks, users, playlists shown</v>
+        <v>No blank/white screen</v>
       </c>
       <c r="I63" t="str">
-        <v>Not tested in e2e run</v>
+        <v>Behaved as expected — assertion passed</v>
       </c>
       <c r="J63" t="str">
-        <v>Not Tested</v>
+        <v>PASS</v>
       </c>
       <c r="K63" t="str">
-        <v>High</v>
+        <v>Critical</v>
       </c>
       <c r="L63" t="str">
         <v/>
       </c>
     </row>
-    <row r="64" xml:space="preserve">
+    <row r="64">
       <c r="A64" t="str">
-        <v>TC-SRCH-02</v>
+        <v>TC-M4-UPL-01</v>
       </c>
       <c r="B64" t="str">
-        <v>Module 8 — Search &amp; Discovery</v>
+        <v>M4 – Tracks</v>
       </c>
       <c r="C64" t="str">
-        <v>Feed</v>
+        <v>Upload</v>
       </c>
       <c r="D64" t="str">
-        <v>Functional – Happy Path</v>
+        <v>Security</v>
       </c>
       <c r="E64" t="str">
-        <v>Authenticated user sees activity feed from followed artists</v>
+        <v>Guest cannot access /upload</v>
       </c>
       <c r="F64" t="str">
-        <v>User follows at least one artist with uploads</v>
-      </c>
-      <c r="G64" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Navigate to home/stream feed
-2. Check feed content</v>
+        <v>Not logged in</v>
+      </c>
+      <c r="G64" t="str">
+        <v>Navigate to /upload</v>
       </c>
       <c r="H64" t="str">
-        <v>Chronological list of tracks from followed users</v>
+        <v>Redirected or gated</v>
       </c>
       <c r="I64" t="str">
-        <v>Not tested in e2e run</v>
+        <v>Behaved as expected — assertion passed</v>
       </c>
       <c r="J64" t="str">
-        <v>Not Tested</v>
+        <v>PASS</v>
       </c>
       <c r="K64" t="str">
-        <v>High</v>
+        <v>Critical</v>
       </c>
       <c r="L64" t="str">
         <v/>
       </c>
     </row>
-    <row r="65" xml:space="preserve">
+    <row r="65">
       <c r="A65" t="str">
-        <v>TC-SRCH-03</v>
+        <v>TC-M4-UPL-02</v>
       </c>
       <c r="B65" t="str">
-        <v>Module 8 — Search &amp; Discovery</v>
+        <v>M4 – Tracks</v>
       </c>
       <c r="C65" t="str">
-        <v>Trending</v>
+        <v>Upload</v>
       </c>
       <c r="D65" t="str">
-        <v>Functional – Happy Path</v>
+        <v>Functional</v>
       </c>
       <c r="E65" t="str">
-        <v>Trending/charts section shows top tracks</v>
+        <v>Upload page renders header and drop zone</v>
       </c>
       <c r="F65" t="str">
-        <v>Play counts exist</v>
-      </c>
-      <c r="G65" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Navigate to /trending
-2. Verify list</v>
+        <v>Logged in</v>
+      </c>
+      <c r="G65" t="str">
+        <v>Navigate to /upload</v>
       </c>
       <c r="H65" t="str">
-        <v>Top tracks ordered by play count / engagement</v>
+        <v>Header and upload zone visible</v>
       </c>
       <c r="I65" t="str">
-        <v>Not tested</v>
+        <v>Behaved as expected — assertion passed</v>
       </c>
       <c r="J65" t="str">
-        <v>Not Tested</v>
+        <v>PASS</v>
       </c>
       <c r="K65" t="str">
+        <v>High</v>
+      </c>
+      <c r="L65" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>TC-M4-UPL-03</v>
+      </c>
+      <c r="B66" t="str">
+        <v>M4 – Tracks</v>
+      </c>
+      <c r="C66" t="str">
+        <v>Upload</v>
+      </c>
+      <c r="D66" t="str">
+        <v>Functional</v>
+      </c>
+      <c r="E66" t="str">
+        <v>File input accepts mp3 and wav</v>
+      </c>
+      <c r="F66" t="str">
+        <v>Logged in, on /upload</v>
+      </c>
+      <c r="G66" t="str">
+        <v>Inspect file input accept attribute</v>
+      </c>
+      <c r="H66" t="str">
+        <v>Accepts audio/mpeg and audio/wav</v>
+      </c>
+      <c r="I66" t="str">
+        <v>Behaved as expected — assertion passed</v>
+      </c>
+      <c r="J66" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="K66" t="str">
+        <v>High</v>
+      </c>
+      <c r="L66" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>TC-M4-UPL-04</v>
+      </c>
+      <c r="B67" t="str">
+        <v>M4 – Tracks</v>
+      </c>
+      <c r="C67" t="str">
+        <v>Upload</v>
+      </c>
+      <c r="D67" t="str">
+        <v>Functional</v>
+      </c>
+      <c r="E67" t="str">
+        <v>Upload shows paywall or upload form</v>
+      </c>
+      <c r="F67" t="str">
+        <v>Logged in</v>
+      </c>
+      <c r="G67" t="str">
+        <v>Open /upload → check state</v>
+      </c>
+      <c r="H67" t="str">
+        <v>Paywall overlay OR upload form shown</v>
+      </c>
+      <c r="I67" t="str">
+        <v>Behaved as expected — assertion passed</v>
+      </c>
+      <c r="J67" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="K67" t="str">
+        <v>High</v>
+      </c>
+      <c r="L67" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>TC-M4-VIS-01</v>
+      </c>
+      <c r="B68" t="str">
+        <v>M4 – Tracks</v>
+      </c>
+      <c r="C68" t="str">
+        <v>My Tracks</v>
+      </c>
+      <c r="D68" t="str">
+        <v>Functional</v>
+      </c>
+      <c r="E68" t="str">
+        <v>My-tracks page renders for authenticated user</v>
+      </c>
+      <c r="F68" t="str">
+        <v>Logged in</v>
+      </c>
+      <c r="G68" t="str">
+        <v>Navigate to /my-tracks</v>
+      </c>
+      <c r="H68" t="str">
+        <v>Track list or empty state</v>
+      </c>
+      <c r="I68" t="str">
+        <v>Behaved as expected — assertion passed</v>
+      </c>
+      <c r="J68" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="K68" t="str">
+        <v>High</v>
+      </c>
+      <c r="L68" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>TC-M4-VIS-02</v>
+      </c>
+      <c r="B69" t="str">
+        <v>M4 – Tracks</v>
+      </c>
+      <c r="C69" t="str">
+        <v>My Tracks</v>
+      </c>
+      <c r="D69" t="str">
+        <v>Security</v>
+      </c>
+      <c r="E69" t="str">
+        <v>Guest cannot access /my-tracks</v>
+      </c>
+      <c r="F69" t="str">
+        <v>Not logged in</v>
+      </c>
+      <c r="G69" t="str">
+        <v>Navigate to /my-tracks</v>
+      </c>
+      <c r="H69" t="str">
+        <v>Redirected or gated</v>
+      </c>
+      <c r="I69" t="str">
+        <v>Behaved as expected — assertion passed</v>
+      </c>
+      <c r="J69" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="K69" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="L69" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>TC-M4-WAV-01</v>
+      </c>
+      <c r="B70" t="str">
+        <v>M4 – Tracks</v>
+      </c>
+      <c r="C70" t="str">
+        <v>Waveform</v>
+      </c>
+      <c r="D70" t="str">
+        <v>UI</v>
+      </c>
+      <c r="E70" t="str">
+        <v>Waveform element renders on track page</v>
+      </c>
+      <c r="F70" t="str">
+        <v>On a track page</v>
+      </c>
+      <c r="G70" t="str">
+        <v>Check waveform element</v>
+      </c>
+      <c r="H70" t="str">
+        <v>Waveform present</v>
+      </c>
+      <c r="I70" t="str">
+        <v>Behaved as expected — assertion passed</v>
+      </c>
+      <c r="J70" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="K70" t="str">
+        <v>High</v>
+      </c>
+      <c r="L70" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>TC-M4-WAV-02</v>
+      </c>
+      <c r="B71" t="str">
+        <v>M4 – Tracks</v>
+      </c>
+      <c r="C71" t="str">
+        <v>Waveform</v>
+      </c>
+      <c r="D71" t="str">
+        <v>UI</v>
+      </c>
+      <c r="E71" t="str">
+        <v>Duration badge renders with time-format text</v>
+      </c>
+      <c r="F71" t="str">
+        <v>On a track page</v>
+      </c>
+      <c r="G71" t="str">
+        <v>Check duration badge</v>
+      </c>
+      <c r="H71" t="str">
+        <v>Badge shows mm:ss or hh:mm:ss</v>
+      </c>
+      <c r="I71" t="str">
+        <v>Behaved as expected — assertion passed</v>
+      </c>
+      <c r="J71" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="K71" t="str">
         <v>Medium</v>
-      </c>
-      <c r="L65" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="66" xml:space="preserve">
-      <c r="A66" t="str">
-        <v>TC-MSG-01</v>
-      </c>
-      <c r="B66" t="str">
-        <v>Module 9 — Messaging</v>
-      </c>
-      <c r="C66" t="str">
-        <v>Send Direct Message</v>
-      </c>
-      <c r="D66" t="str">
-        <v>Functional – Happy Path</v>
-      </c>
-      <c r="E66" t="str">
-        <v>User sends a text message to another user</v>
-      </c>
-      <c r="F66" t="str">
-        <v>Both users exist; not blocked</v>
-      </c>
-      <c r="G66" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Navigate to /messages/:userId
-2. Type message
-3. Send</v>
-      </c>
-      <c r="H66" t="str">
-        <v>Message delivered and displayed in thread</v>
-      </c>
-      <c r="I66" t="str">
-        <v>Not tested</v>
-      </c>
-      <c r="J66" t="str">
-        <v>Not Tested</v>
-      </c>
-      <c r="K66" t="str">
-        <v>High</v>
-      </c>
-      <c r="L66" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="67" xml:space="preserve">
-      <c r="A67" t="str">
-        <v>TC-MSG-02</v>
-      </c>
-      <c r="B67" t="str">
-        <v>Module 9 — Messaging</v>
-      </c>
-      <c r="C67" t="str">
-        <v>Unread Count</v>
-      </c>
-      <c r="D67" t="str">
-        <v>Functional – Happy Path</v>
-      </c>
-      <c r="E67" t="str">
-        <v>Unread message count updates on new message</v>
-      </c>
-      <c r="F67" t="str">
-        <v>User has unread messages</v>
-      </c>
-      <c r="G67" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Receive message
-2. Check notification badge</v>
-      </c>
-      <c r="H67" t="str">
-        <v>Badge shows correct unread count</v>
-      </c>
-      <c r="I67" t="str">
-        <v>Not tested</v>
-      </c>
-      <c r="J67" t="str">
-        <v>Not Tested</v>
-      </c>
-      <c r="K67" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="L67" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="68" xml:space="preserve">
-      <c r="A68" t="str">
-        <v>TC-NOTIF-01</v>
-      </c>
-      <c r="B68" t="str">
-        <v>Module 10 — Notifications</v>
-      </c>
-      <c r="C68" t="str">
-        <v>Like Notification</v>
-      </c>
-      <c r="D68" t="str">
-        <v>Functional – Happy Path</v>
-      </c>
-      <c r="E68" t="str">
-        <v>User receives notification when their track is liked</v>
-      </c>
-      <c r="F68" t="str">
-        <v>Track exists; another user likes it</v>
-      </c>
-      <c r="G68" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. User A likes User B track
-2. User B checks notifications</v>
-      </c>
-      <c r="H68" t="str">
-        <v>Notification: "User A liked your track" appears</v>
-      </c>
-      <c r="I68" t="str">
-        <v>Not tested</v>
-      </c>
-      <c r="J68" t="str">
-        <v>Not Tested</v>
-      </c>
-      <c r="K68" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="L68" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="69" xml:space="preserve">
-      <c r="A69" t="str">
-        <v>TC-NOTIF-02</v>
-      </c>
-      <c r="B69" t="str">
-        <v>Module 10 — Notifications</v>
-      </c>
-      <c r="C69" t="str">
-        <v>Mark All Read</v>
-      </c>
-      <c r="D69" t="str">
-        <v>Functional – Happy Path</v>
-      </c>
-      <c r="E69" t="str">
-        <v>Mark all notifications as read clears unread counter</v>
-      </c>
-      <c r="F69" t="str">
-        <v>Unread notifications exist</v>
-      </c>
-      <c r="G69" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Click "Mark all as read"
-2. Check counter</v>
-      </c>
-      <c r="H69" t="str">
-        <v>Counter reset to 0; all notifications marked read</v>
-      </c>
-      <c r="I69" t="str">
-        <v>Not tested</v>
-      </c>
-      <c r="J69" t="str">
-        <v>Not Tested</v>
-      </c>
-      <c r="K69" t="str">
-        <v>Low</v>
-      </c>
-      <c r="L69" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="70" xml:space="preserve">
-      <c r="A70" t="str">
-        <v>TC-ADM-01</v>
-      </c>
-      <c r="B70" t="str">
-        <v>Module 11 — Admin</v>
-      </c>
-      <c r="C70" t="str">
-        <v>Report System</v>
-      </c>
-      <c r="D70" t="str">
-        <v>Functional – Happy Path</v>
-      </c>
-      <c r="E70" t="str">
-        <v>User reports a track for copyright violation</v>
-      </c>
-      <c r="F70" t="str">
-        <v>Track exists; user authenticated</v>
-      </c>
-      <c r="G70" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Click Report on track
-2. Select Copyright
-3. Submit</v>
-      </c>
-      <c r="H70" t="str">
-        <v>Report submitted; confirmation shown</v>
-      </c>
-      <c r="I70" t="str">
-        <v>Not tested</v>
-      </c>
-      <c r="J70" t="str">
-        <v>Not Tested</v>
-      </c>
-      <c r="K70" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="L70" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="71" xml:space="preserve">
-      <c r="A71" t="str">
-        <v>TC-ADM-02</v>
-      </c>
-      <c r="B71" t="str">
-        <v>Module 11 — Admin</v>
-      </c>
-      <c r="C71" t="str">
-        <v>Admin — Suspend Account</v>
-      </c>
-      <c r="D71" t="str">
-        <v>Functional – Admin</v>
-      </c>
-      <c r="E71" t="str">
-        <v>Admin suspends a user account</v>
-      </c>
-      <c r="F71" t="str">
-        <v>Admin dashboard accessible</v>
-      </c>
-      <c r="G71" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Log in as admin
-2. Find user
-3. Click Suspend</v>
-      </c>
-      <c r="H71" t="str">
-        <v>Account suspended; user cannot log in</v>
-      </c>
-      <c r="I71" t="str">
-        <v>Not tested</v>
-      </c>
-      <c r="J71" t="str">
-        <v>Not Tested</v>
-      </c>
-      <c r="K71" t="str">
-        <v>High</v>
       </c>
       <c r="L71" t="str">
         <v/>
@@ -3177,34 +3117,34 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>TC-PREM-01</v>
+        <v>TC-M5-ACC-01</v>
       </c>
       <c r="B72" t="str">
-        <v>Module 12 — Premium</v>
+        <v>M5 – Playback</v>
       </c>
       <c r="C72" t="str">
-        <v>Upload Limit – Free</v>
+        <v>Access Tiers</v>
       </c>
       <c r="D72" t="str">
-        <v>Functional – Happy Path</v>
+        <v>Functional</v>
       </c>
       <c r="E72" t="str">
-        <v>Free user is blocked after uploading 3 tracks</v>
+        <v>Playback state chip renders (Playable/Preview/Blocked)</v>
       </c>
       <c r="F72" t="str">
-        <v>Free user has 3 existing uploads</v>
+        <v>On a track page</v>
       </c>
       <c r="G72" t="str">
-        <v>1. Attempt 4th upload as free user</v>
+        <v>Open /tracks/:id → check state chip</v>
       </c>
       <c r="H72" t="str">
-        <v>Paywall shown; upload blocked with upgrade prompt</v>
+        <v>Chip shows valid state</v>
       </c>
       <c r="I72" t="str">
-        <v>Not tested</v>
+        <v>Behaved as expected — assertion passed</v>
       </c>
       <c r="J72" t="str">
-        <v>Not Tested</v>
+        <v>PASS</v>
       </c>
       <c r="K72" t="str">
         <v>High</v>
@@ -3213,111 +3153,2650 @@
         <v/>
       </c>
     </row>
-    <row r="73" xml:space="preserve">
+    <row r="73">
       <c r="A73" t="str">
-        <v>TC-PREM-02</v>
+        <v>TC-M5-ACC-02</v>
       </c>
       <c r="B73" t="str">
-        <v>Module 12 — Premium</v>
+        <v>M5 – Playback</v>
       </c>
       <c r="C73" t="str">
-        <v>Stripe Subscription Mock</v>
+        <v>Access Tiers</v>
       </c>
       <c r="D73" t="str">
-        <v>Functional – Happy Path</v>
+        <v>Robustness</v>
       </c>
       <c r="E73" t="str">
-        <v>User completes mock Stripe payment and gains Pro tier</v>
+        <v>Track page handles any playback tier without crash</v>
       </c>
       <c r="F73" t="str">
-        <v>User on subscription page</v>
-      </c>
-      <c r="G73" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Click Upgrade
-2. Enter mock card details
-3. Confirm</v>
+        <v>On a track page</v>
+      </c>
+      <c r="G73" t="str">
+        <v>Open track page</v>
       </c>
       <c r="H73" t="str">
-        <v>Subscription active; unlimited uploads unlocked</v>
+        <v>No JS error on load</v>
       </c>
       <c r="I73" t="str">
-        <v>Not tested</v>
+        <v>Behaved as expected — assertion passed</v>
       </c>
       <c r="J73" t="str">
-        <v>Not Tested</v>
+        <v>PASS</v>
       </c>
       <c r="K73" t="str">
         <v>High</v>
       </c>
       <c r="L73" t="str">
-        <v>Stripe is mocked</v>
-      </c>
-    </row>
-    <row r="74" xml:space="preserve">
+        <v/>
+      </c>
+    </row>
+    <row r="74">
       <c r="A74" t="str">
-        <v>TC-PREM-03</v>
+        <v>TC-M5-HIS-01</v>
       </c>
       <c r="B74" t="str">
-        <v>Module 12 — Premium</v>
+        <v>M5 – Playback</v>
       </c>
       <c r="C74" t="str">
-        <v>Ad-Free Experience</v>
+        <v>History</v>
       </c>
       <c r="D74" t="str">
-        <v>Functional – Happy Path</v>
+        <v>Functional</v>
       </c>
       <c r="E74" t="str">
-        <v>Pro user does not see ads during playback</v>
+        <v>/history page renders playback history section</v>
       </c>
       <c r="F74" t="str">
-        <v>Pro subscription active</v>
-      </c>
-      <c r="G74" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Log in as Pro user
-2. Play tracks</v>
+        <v>Logged in</v>
+      </c>
+      <c r="G74" t="str">
+        <v>Navigate to /history</v>
       </c>
       <c r="H74" t="str">
-        <v>No ad banners or interruptions</v>
+        <v>History section visible</v>
       </c>
       <c r="I74" t="str">
-        <v>Not tested</v>
+        <v>Behaved as expected — assertion passed</v>
       </c>
       <c r="J74" t="str">
-        <v>Not Tested</v>
+        <v>PASS</v>
       </c>
       <c r="K74" t="str">
+        <v>High</v>
+      </c>
+      <c r="L74" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>TC-M5-HIS-02</v>
+      </c>
+      <c r="B75" t="str">
+        <v>M5 – Playback</v>
+      </c>
+      <c r="C75" t="str">
+        <v>History</v>
+      </c>
+      <c r="D75" t="str">
+        <v>Functional</v>
+      </c>
+      <c r="E75" t="str">
+        <v>Recently played shows cards or empty state</v>
+      </c>
+      <c r="F75" t="str">
+        <v>On /history</v>
+      </c>
+      <c r="G75" t="str">
+        <v>Check recently played grid</v>
+      </c>
+      <c r="H75" t="str">
+        <v>Cards or empty state shown</v>
+      </c>
+      <c r="I75" t="str">
+        <v>Behaved as expected — assertion passed</v>
+      </c>
+      <c r="J75" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="K75" t="str">
+        <v>High</v>
+      </c>
+      <c r="L75" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>TC-M5-HIS-03</v>
+      </c>
+      <c r="B76" t="str">
+        <v>M5 – Playback</v>
+      </c>
+      <c r="C76" t="str">
+        <v>History</v>
+      </c>
+      <c r="D76" t="str">
+        <v>UI</v>
+      </c>
+      <c r="E76" t="str">
+        <v>Filter input visible on history page</v>
+      </c>
+      <c r="F76" t="str">
+        <v>On /history</v>
+      </c>
+      <c r="G76" t="str">
+        <v>Check filter input</v>
+      </c>
+      <c r="H76" t="str">
+        <v>Filter/search input visible</v>
+      </c>
+      <c r="I76" t="str">
+        <v>Behaved as expected — assertion passed</v>
+      </c>
+      <c r="J76" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="K76" t="str">
         <v>Medium</v>
       </c>
-      <c r="L74" t="str">
+      <c r="L76" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>TC-M5-RSP-01</v>
+      </c>
+      <c r="B77" t="str">
+        <v>M5 – Playback</v>
+      </c>
+      <c r="C77" t="str">
+        <v>Persistent Player</v>
+      </c>
+      <c r="D77" t="str">
+        <v>Functional</v>
+      </c>
+      <c r="E77" t="str">
+        <v>Player bar persists after navigating away from track</v>
+      </c>
+      <c r="F77" t="str">
+        <v>Track playing</v>
+      </c>
+      <c r="G77" t="str">
+        <v>Play track → navigate to home → check bar</v>
+      </c>
+      <c r="H77" t="str">
+        <v>Player bar still visible</v>
+      </c>
+      <c r="I77" t="str">
+        <v>Behaved as expected — assertion passed</v>
+      </c>
+      <c r="J77" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="K77" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="L77" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>TC-M5-STR-01</v>
+      </c>
+      <c r="B78" t="str">
+        <v>M5 – Playback</v>
+      </c>
+      <c r="C78" t="str">
+        <v>Streaming</v>
+      </c>
+      <c r="D78" t="str">
+        <v>UI</v>
+      </c>
+      <c r="E78" t="str">
+        <v>Play button visible on track hero</v>
+      </c>
+      <c r="F78" t="str">
+        <v>On a track page</v>
+      </c>
+      <c r="G78" t="str">
+        <v>Check hero play button</v>
+      </c>
+      <c r="H78" t="str">
+        <v>Play button visible</v>
+      </c>
+      <c r="I78" t="str">
+        <v>Behaved as expected — assertion passed</v>
+      </c>
+      <c r="J78" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="K78" t="str">
+        <v>High</v>
+      </c>
+      <c r="L78" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>TC-M5-STR-02</v>
+      </c>
+      <c r="B79" t="str">
+        <v>M5 – Playback</v>
+      </c>
+      <c r="C79" t="str">
+        <v>Streaming</v>
+      </c>
+      <c r="D79" t="str">
+        <v>Functional</v>
+      </c>
+      <c r="E79" t="str">
+        <v>Clicking play changes hero to is-playing state</v>
+      </c>
+      <c r="F79" t="str">
+        <v>On a track page</v>
+      </c>
+      <c r="G79" t="str">
+        <v>Click play → check state class</v>
+      </c>
+      <c r="H79" t="str">
+        <v>Hero has is-playing state</v>
+      </c>
+      <c r="I79" t="str">
+        <v>Behaved as expected — assertion passed</v>
+      </c>
+      <c r="J79" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="K79" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="L79" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>TC-M5-STR-03</v>
+      </c>
+      <c r="B80" t="str">
+        <v>M5 – Playback</v>
+      </c>
+      <c r="C80" t="str">
+        <v>Seeking</v>
+      </c>
+      <c r="D80" t="str">
+        <v>Functional</v>
+      </c>
+      <c r="E80" t="str">
+        <v>Waveform present and interactive for seeking</v>
+      </c>
+      <c r="F80" t="str">
+        <v>On a track page</v>
+      </c>
+      <c r="G80" t="str">
+        <v>Check waveform interactivity</v>
+      </c>
+      <c r="H80" t="str">
+        <v>Waveform visible and clickable</v>
+      </c>
+      <c r="I80" t="str">
+        <v>Behaved as expected — assertion passed</v>
+      </c>
+      <c r="J80" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="K80" t="str">
+        <v>High</v>
+      </c>
+      <c r="L80" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v>TC-M5-STR-04</v>
+      </c>
+      <c r="B81" t="str">
+        <v>M5 – Playback</v>
+      </c>
+      <c r="C81" t="str">
+        <v>Persistent Player</v>
+      </c>
+      <c r="D81" t="str">
+        <v>UI</v>
+      </c>
+      <c r="E81" t="str">
+        <v>Persistent player bar present on the page</v>
+      </c>
+      <c r="F81" t="str">
+        <v>Track playing</v>
+      </c>
+      <c r="G81" t="str">
+        <v>Play track → check player bar</v>
+      </c>
+      <c r="H81" t="str">
+        <v>Player bar visible at bottom</v>
+      </c>
+      <c r="I81" t="str">
+        <v>Behaved as expected — assertion passed</v>
+      </c>
+      <c r="J81" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="K81" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="L81" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>TC-M6-CMT-01</v>
+      </c>
+      <c r="B82" t="str">
+        <v>M6 – Engagement</v>
+      </c>
+      <c r="C82" t="str">
+        <v>Comments</v>
+      </c>
+      <c r="D82" t="str">
+        <v>UI</v>
+      </c>
+      <c r="E82" t="str">
+        <v>Comment input bar visible on track page</v>
+      </c>
+      <c r="F82" t="str">
+        <v>On a track page</v>
+      </c>
+      <c r="G82" t="str">
+        <v>Check comment input</v>
+      </c>
+      <c r="H82" t="str">
+        <v>Comment input visible</v>
+      </c>
+      <c r="I82" t="str">
+        <v>Behaved as expected — assertion passed</v>
+      </c>
+      <c r="J82" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="K82" t="str">
+        <v>High</v>
+      </c>
+      <c r="L82" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>TC-M6-CMT-02</v>
+      </c>
+      <c r="B83" t="str">
+        <v>M6 – Engagement</v>
+      </c>
+      <c r="C83" t="str">
+        <v>Comments</v>
+      </c>
+      <c r="D83" t="str">
+        <v>Security</v>
+      </c>
+      <c r="E83" t="str">
+        <v>Comment submission blocked for unauthenticated</v>
+      </c>
+      <c r="F83" t="str">
+        <v>Not logged in</v>
+      </c>
+      <c r="G83" t="str">
+        <v>Try submitting comment without auth</v>
+      </c>
+      <c r="H83" t="str">
+        <v>Blocked or auth-gated</v>
+      </c>
+      <c r="I83" t="str">
+        <v>Behaved as expected — assertion passed</v>
+      </c>
+      <c r="J83" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="K83" t="str">
+        <v>High</v>
+      </c>
+      <c r="L83" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>TC-M6-CMT-03</v>
+      </c>
+      <c r="B84" t="str">
+        <v>M6 – Engagement</v>
+      </c>
+      <c r="C84" t="str">
+        <v>Comments</v>
+      </c>
+      <c r="D84" t="str">
+        <v>Functional</v>
+      </c>
+      <c r="E84" t="str">
+        <v>Comments panel renders thread or empty state</v>
+      </c>
+      <c r="F84" t="str">
+        <v>On a track page</v>
+      </c>
+      <c r="G84" t="str">
+        <v>Check comments panel</v>
+      </c>
+      <c r="H84" t="str">
+        <v>Thread or empty state shown</v>
+      </c>
+      <c r="I84" t="str">
+        <v>Behaved as expected — assertion passed</v>
+      </c>
+      <c r="J84" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="K84" t="str">
+        <v>High</v>
+      </c>
+      <c r="L84" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>TC-M6-CMT-04</v>
+      </c>
+      <c r="B85" t="str">
+        <v>M6 – Engagement</v>
+      </c>
+      <c r="C85" t="str">
+        <v>Comments</v>
+      </c>
+      <c r="D85" t="str">
+        <v>UI</v>
+      </c>
+      <c r="E85" t="str">
+        <v>Timestamp checkbox visible in comment composer</v>
+      </c>
+      <c r="F85" t="str">
+        <v>Logged in, track page</v>
+      </c>
+      <c r="G85" t="str">
+        <v>Check composer for timestamp checkbox</v>
+      </c>
+      <c r="H85" t="str">
+        <v>Checkbox visible</v>
+      </c>
+      <c r="I85" t="str">
+        <v>Behaved as expected — assertion passed</v>
+      </c>
+      <c r="J85" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="K85" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="L85" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>TC-M6-ENG-01</v>
+      </c>
+      <c r="B86" t="str">
+        <v>M6 – Engagement</v>
+      </c>
+      <c r="C86" t="str">
+        <v>Likes</v>
+      </c>
+      <c r="D86" t="str">
+        <v>Functional</v>
+      </c>
+      <c r="E86" t="str">
+        <v>/tracks/:id/likes renders section panel</v>
+      </c>
+      <c r="F86" t="str">
+        <v>Logged in</v>
+      </c>
+      <c r="G86" t="str">
+        <v>Navigate to /tracks/:id/likes</v>
+      </c>
+      <c r="H86" t="str">
+        <v>Likes panel renders</v>
+      </c>
+      <c r="I86" t="str">
+        <v>Behaved as expected — assertion passed</v>
+      </c>
+      <c r="J86" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="K86" t="str">
+        <v>High</v>
+      </c>
+      <c r="L86" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>TC-M6-ENG-02</v>
+      </c>
+      <c r="B87" t="str">
+        <v>M6 – Engagement</v>
+      </c>
+      <c r="C87" t="str">
+        <v>Reposts</v>
+      </c>
+      <c r="D87" t="str">
+        <v>Functional</v>
+      </c>
+      <c r="E87" t="str">
+        <v>/tracks/:id/reposts renders section panel</v>
+      </c>
+      <c r="F87" t="str">
+        <v>Logged in</v>
+      </c>
+      <c r="G87" t="str">
+        <v>Navigate to /tracks/:id/reposts</v>
+      </c>
+      <c r="H87" t="str">
+        <v>Reposts panel renders</v>
+      </c>
+      <c r="I87" t="str">
+        <v>Behaved as expected — assertion passed</v>
+      </c>
+      <c r="J87" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="K87" t="str">
+        <v>High</v>
+      </c>
+      <c r="L87" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>TC-M6-LIK-01</v>
+      </c>
+      <c r="B88" t="str">
+        <v>M6 – Engagement</v>
+      </c>
+      <c r="C88" t="str">
+        <v>Likes</v>
+      </c>
+      <c r="D88" t="str">
+        <v>UI</v>
+      </c>
+      <c r="E88" t="str">
+        <v>Like button visible in track actions row</v>
+      </c>
+      <c r="F88" t="str">
+        <v>On a track page</v>
+      </c>
+      <c r="G88" t="str">
+        <v>Check track actions row</v>
+      </c>
+      <c r="H88" t="str">
+        <v>Like button present</v>
+      </c>
+      <c r="I88" t="str">
+        <v>Behaved as expected — assertion passed</v>
+      </c>
+      <c r="J88" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="K88" t="str">
+        <v>High</v>
+      </c>
+      <c r="L88" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>TC-M6-LIK-02</v>
+      </c>
+      <c r="B89" t="str">
+        <v>M6 – Engagement</v>
+      </c>
+      <c r="C89" t="str">
+        <v>Likes</v>
+      </c>
+      <c r="D89" t="str">
+        <v>Functional</v>
+      </c>
+      <c r="E89" t="str">
+        <v>Like button is clickable</v>
+      </c>
+      <c r="F89" t="str">
+        <v>Logged in, track page</v>
+      </c>
+      <c r="G89" t="str">
+        <v>Click like button</v>
+      </c>
+      <c r="H89" t="str">
+        <v>Click interaction fires</v>
+      </c>
+      <c r="I89" t="str">
+        <v>Behaved as expected — assertion passed</v>
+      </c>
+      <c r="J89" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="K89" t="str">
+        <v>High</v>
+      </c>
+      <c r="L89" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>TC-M6-LIK-03</v>
+      </c>
+      <c r="B90" t="str">
+        <v>M6 – Engagement</v>
+      </c>
+      <c r="C90" t="str">
+        <v>Likes</v>
+      </c>
+      <c r="D90" t="str">
+        <v>UI</v>
+      </c>
+      <c r="E90" t="str">
+        <v>Like count visible on track page</v>
+      </c>
+      <c r="F90" t="str">
+        <v>On a track page</v>
+      </c>
+      <c r="G90" t="str">
+        <v>Check stat row</v>
+      </c>
+      <c r="H90" t="str">
+        <v>Like count/stat visible</v>
+      </c>
+      <c r="I90" t="str">
+        <v>Behaved as expected — assertion passed</v>
+      </c>
+      <c r="J90" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="K90" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="L90" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>TC-M6-REP-01</v>
+      </c>
+      <c r="B91" t="str">
+        <v>M6 – Engagement</v>
+      </c>
+      <c r="C91" t="str">
+        <v>Reposts</v>
+      </c>
+      <c r="D91" t="str">
+        <v>UI</v>
+      </c>
+      <c r="E91" t="str">
+        <v>Repost button visible in track actions row</v>
+      </c>
+      <c r="F91" t="str">
+        <v>On a track page</v>
+      </c>
+      <c r="G91" t="str">
+        <v>Check track actions row</v>
+      </c>
+      <c r="H91" t="str">
+        <v>Repost button present</v>
+      </c>
+      <c r="I91" t="str">
+        <v>Behaved as expected — assertion passed</v>
+      </c>
+      <c r="J91" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="K91" t="str">
+        <v>High</v>
+      </c>
+      <c r="L91" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>TC-M6-REP-02</v>
+      </c>
+      <c r="B92" t="str">
+        <v>M6 – Engagement</v>
+      </c>
+      <c r="C92" t="str">
+        <v>Reposts</v>
+      </c>
+      <c r="D92" t="str">
+        <v>Functional</v>
+      </c>
+      <c r="E92" t="str">
+        <v>Repost button is clickable</v>
+      </c>
+      <c r="F92" t="str">
+        <v>Logged in, track page</v>
+      </c>
+      <c r="G92" t="str">
+        <v>Click repost button</v>
+      </c>
+      <c r="H92" t="str">
+        <v>Click interaction fires</v>
+      </c>
+      <c r="I92" t="str">
+        <v>Behaved as expected — assertion passed</v>
+      </c>
+      <c r="J92" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="K92" t="str">
+        <v>High</v>
+      </c>
+      <c r="L92" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>TC-M7-CRU-01</v>
+      </c>
+      <c r="B93" t="str">
+        <v>M7 – Playlists</v>
+      </c>
+      <c r="C93" t="str">
+        <v>Artist Studio</v>
+      </c>
+      <c r="D93" t="str">
+        <v>Functional</v>
+      </c>
+      <c r="E93" t="str">
+        <v>Artist Studio renders with track list</v>
+      </c>
+      <c r="F93" t="str">
+        <v>Logged in</v>
+      </c>
+      <c r="G93" t="str">
+        <v>Navigate to /my-tracks</v>
+      </c>
+      <c r="H93" t="str">
+        <v>Track list or handled state</v>
+      </c>
+      <c r="I93" t="str">
+        <v>Behaved as expected — assertion passed</v>
+      </c>
+      <c r="J93" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="K93" t="str">
+        <v>High</v>
+      </c>
+      <c r="L93" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v>TC-M7-CRU-02</v>
+      </c>
+      <c r="B94" t="str">
+        <v>M7 – Playlists</v>
+      </c>
+      <c r="C94" t="str">
+        <v>Add to Playlist</v>
+      </c>
+      <c r="D94" t="str">
+        <v>Functional</v>
+      </c>
+      <c r="E94" t="str">
+        <v>Add-to-playlist shows playlists or create option</v>
+      </c>
+      <c r="F94" t="str">
+        <v>Logged in, track page</v>
+      </c>
+      <c r="G94" t="str">
+        <v>Open add-to-playlist panel</v>
+      </c>
+      <c r="H94" t="str">
+        <v>Existing playlists or "Create" option</v>
+      </c>
+      <c r="I94" t="str">
+        <v>Behaved as expected — assertion passed</v>
+      </c>
+      <c r="J94" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="K94" t="str">
+        <v>High</v>
+      </c>
+      <c r="L94" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>TC-M7-CRU-03</v>
+      </c>
+      <c r="B95" t="str">
+        <v>M7 – Playlists</v>
+      </c>
+      <c r="C95" t="str">
+        <v>Auth Guard</v>
+      </c>
+      <c r="D95" t="str">
+        <v>Security</v>
+      </c>
+      <c r="E95" t="str">
+        <v>Guest cannot access Artist Studio</v>
+      </c>
+      <c r="F95" t="str">
+        <v>Not logged in</v>
+      </c>
+      <c r="G95" t="str">
+        <v>Navigate to /my-tracks</v>
+      </c>
+      <c r="H95" t="str">
+        <v>Redirected or gated</v>
+      </c>
+      <c r="I95" t="str">
+        <v>Behaved as expected — assertion passed</v>
+      </c>
+      <c r="J95" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="K95" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="L95" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v>TC-M7-CRU-04</v>
+      </c>
+      <c r="B96" t="str">
+        <v>M7 – Playlists</v>
+      </c>
+      <c r="C96" t="str">
+        <v>Create Playlist</v>
+      </c>
+      <c r="D96" t="str">
+        <v>Functional</v>
+      </c>
+      <c r="E96" t="str">
+        <v>Create playlist form has title and privacy</v>
+      </c>
+      <c r="F96" t="str">
+        <v>Logged in</v>
+      </c>
+      <c r="G96" t="str">
+        <v>Open create playlist form</v>
+      </c>
+      <c r="H96" t="str">
+        <v>Title input and privacy options visible</v>
+      </c>
+      <c r="I96" t="str">
+        <v>Behaved as expected — assertion passed</v>
+      </c>
+      <c r="J96" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="K96" t="str">
+        <v>High</v>
+      </c>
+      <c r="L96" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v>TC-M7-DET-01</v>
+      </c>
+      <c r="B97" t="str">
+        <v>M7 – Playlists</v>
+      </c>
+      <c r="C97" t="str">
+        <v>Add to Playlist</v>
+      </c>
+      <c r="D97" t="str">
+        <v>Functional</v>
+      </c>
+      <c r="E97" t="str">
+        <v>Add-to-playlist panel opens and shows options</v>
+      </c>
+      <c r="F97" t="str">
+        <v>Logged in, track page</v>
+      </c>
+      <c r="G97" t="str">
+        <v>Open add-to-playlist panel</v>
+      </c>
+      <c r="H97" t="str">
+        <v>Panel with playlists or create option</v>
+      </c>
+      <c r="I97" t="str">
+        <v>Behaved as expected — assertion passed</v>
+      </c>
+      <c r="J97" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="K97" t="str">
+        <v>High</v>
+      </c>
+      <c r="L97" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
+        <v>TC-M7-DET-02</v>
+      </c>
+      <c r="B98" t="str">
+        <v>M7 – Playlists</v>
+      </c>
+      <c r="C98" t="str">
+        <v>Add to Playlist</v>
+      </c>
+      <c r="D98" t="str">
+        <v>Functional</v>
+      </c>
+      <c r="E98" t="str">
+        <v>Creating playlist and adding track shows confirmation</v>
+      </c>
+      <c r="F98" t="str">
+        <v>Logged in</v>
+      </c>
+      <c r="G98" t="str">
+        <v>Create playlist → add track</v>
+      </c>
+      <c r="H98" t="str">
+        <v>Success confirmation shown</v>
+      </c>
+      <c r="I98" t="str">
+        <v>Behaved as expected — assertion passed</v>
+      </c>
+      <c r="J98" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="K98" t="str">
+        <v>High</v>
+      </c>
+      <c r="L98" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>TC-M7-DET-03</v>
+      </c>
+      <c r="B99" t="str">
+        <v>M7 – Playlists</v>
+      </c>
+      <c r="C99" t="str">
+        <v>Add to Playlist</v>
+      </c>
+      <c r="D99" t="str">
+        <v>Functional</v>
+      </c>
+      <c r="E99" t="str">
+        <v>Panel shows per-playlist action buttons</v>
+      </c>
+      <c r="F99" t="str">
+        <v>Has playlists</v>
+      </c>
+      <c r="G99" t="str">
+        <v>Open add-to-playlist panel</v>
+      </c>
+      <c r="H99" t="str">
+        <v>Action buttons per playlist</v>
+      </c>
+      <c r="I99" t="str">
+        <v>Behaved as expected — assertion passed</v>
+      </c>
+      <c r="J99" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="K99" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="L99" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
+        <v>TC-M7-EMB-01</v>
+      </c>
+      <c r="B100" t="str">
+        <v>M7 – Playlists</v>
+      </c>
+      <c r="C100" t="str">
+        <v>Sharing</v>
+      </c>
+      <c r="D100" t="str">
+        <v>Functional</v>
+      </c>
+      <c r="E100" t="str">
+        <v>Track context menu exposes Copy link</v>
+      </c>
+      <c r="F100" t="str">
+        <v>On a track page</v>
+      </c>
+      <c r="G100" t="str">
+        <v>Open track share menu</v>
+      </c>
+      <c r="H100" t="str">
+        <v>"Copy link" action present</v>
+      </c>
+      <c r="I100" t="str">
+        <v>Behaved as expected — assertion passed</v>
+      </c>
+      <c r="J100" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="K100" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="L100" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v>TC-M7-PRV-01</v>
+      </c>
+      <c r="B101" t="str">
+        <v>M7 – Playlists</v>
+      </c>
+      <c r="C101" t="str">
+        <v>Privacy</v>
+      </c>
+      <c r="D101" t="str">
+        <v>Functional</v>
+      </c>
+      <c r="E101" t="str">
+        <v>Create form offers Public and Private options</v>
+      </c>
+      <c r="F101" t="str">
+        <v>Create form open</v>
+      </c>
+      <c r="G101" t="str">
+        <v>Check privacy options</v>
+      </c>
+      <c r="H101" t="str">
+        <v>Both Public and Private available</v>
+      </c>
+      <c r="I101" t="str">
+        <v>Behaved as expected — assertion passed</v>
+      </c>
+      <c r="J101" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="K101" t="str">
+        <v>High</v>
+      </c>
+      <c r="L101" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>TC-M7-PRV-02</v>
+      </c>
+      <c r="B102" t="str">
+        <v>M7 – Playlists</v>
+      </c>
+      <c r="C102" t="str">
+        <v>Privacy</v>
+      </c>
+      <c r="D102" t="str">
+        <v>Functional</v>
+      </c>
+      <c r="E102" t="str">
+        <v>Selecting Private and saving works</v>
+      </c>
+      <c r="F102" t="str">
+        <v>Create form open</v>
+      </c>
+      <c r="G102" t="str">
+        <v>Select Private → save</v>
+      </c>
+      <c r="H102" t="str">
+        <v>Private playlist created</v>
+      </c>
+      <c r="I102" t="str">
+        <v>Behaved as expected — assertion passed</v>
+      </c>
+      <c r="J102" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="K102" t="str">
+        <v>High</v>
+      </c>
+      <c r="L102" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>TC-M8-FED-01</v>
+      </c>
+      <c r="B103" t="str">
+        <v>M8 – Discovery</v>
+      </c>
+      <c r="C103" t="str">
+        <v>Feed</v>
+      </c>
+      <c r="D103" t="str">
+        <v>Functional</v>
+      </c>
+      <c r="E103" t="str">
+        <v>/feed renders activity feed</v>
+      </c>
+      <c r="F103" t="str">
+        <v>Logged in</v>
+      </c>
+      <c r="G103" t="str">
+        <v>Navigate to /feed</v>
+      </c>
+      <c r="H103" t="str">
+        <v>Feed page renders</v>
+      </c>
+      <c r="I103" t="str">
+        <v>Behaved as expected — assertion passed</v>
+      </c>
+      <c r="J103" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="K103" t="str">
+        <v>High</v>
+      </c>
+      <c r="L103" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>TC-M8-FED-02</v>
+      </c>
+      <c r="B104" t="str">
+        <v>M8 – Discovery</v>
+      </c>
+      <c r="C104" t="str">
+        <v>Feed</v>
+      </c>
+      <c r="D104" t="str">
+        <v>Functional</v>
+      </c>
+      <c r="E104" t="str">
+        <v>Feed shows track cards or follow-prompt</v>
+      </c>
+      <c r="F104" t="str">
+        <v>Logged in, on /feed</v>
+      </c>
+      <c r="G104" t="str">
+        <v>Check feed content</v>
+      </c>
+      <c r="H104" t="str">
+        <v>Cards or follow-prompt/empty state</v>
+      </c>
+      <c r="I104" t="str">
+        <v>Behaved as expected — assertion passed</v>
+      </c>
+      <c r="J104" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="K104" t="str">
+        <v>High</v>
+      </c>
+      <c r="L104" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v>TC-M8-FED-03</v>
+      </c>
+      <c r="B105" t="str">
+        <v>M8 – Discovery</v>
+      </c>
+      <c r="C105" t="str">
+        <v>Discover</v>
+      </c>
+      <c r="D105" t="str">
+        <v>Functional</v>
+      </c>
+      <c r="E105" t="str">
+        <v>/discover renders discover shelf layout</v>
+      </c>
+      <c r="F105" t="str">
+        <v>Logged in</v>
+      </c>
+      <c r="G105" t="str">
+        <v>Navigate to /discover</v>
+      </c>
+      <c r="H105" t="str">
+        <v>Discover shelf visible</v>
+      </c>
+      <c r="I105" t="str">
+        <v>Behaved as expected — assertion passed</v>
+      </c>
+      <c r="J105" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="K105" t="str">
+        <v>High</v>
+      </c>
+      <c r="L105" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v>TC-M8-RES-01</v>
+      </c>
+      <c r="B106" t="str">
+        <v>M8 – Discovery</v>
+      </c>
+      <c r="C106" t="str">
+        <v>Routing</v>
+      </c>
+      <c r="D106" t="str">
+        <v>Robustness</v>
+      </c>
+      <c r="E106" t="str">
+        <v>Wildcard route handles unknown paths gracefully</v>
+      </c>
+      <c r="F106" t="str">
+        <v>App running</v>
+      </c>
+      <c r="G106" t="str">
+        <v>Navigate to /unknown-path-xyz</v>
+      </c>
+      <c r="H106" t="str">
+        <v>404 or graceful fallback</v>
+      </c>
+      <c r="I106" t="str">
+        <v>Behaved as expected — assertion passed</v>
+      </c>
+      <c r="J106" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="K106" t="str">
+        <v>High</v>
+      </c>
+      <c r="L106" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v>TC-M8-SRC-01</v>
+      </c>
+      <c r="B107" t="str">
+        <v>M8 – Discovery</v>
+      </c>
+      <c r="C107" t="str">
+        <v>Search</v>
+      </c>
+      <c r="D107" t="str">
+        <v>Functional</v>
+      </c>
+      <c r="E107" t="str">
+        <v>/search renders input and filter sidebar</v>
+      </c>
+      <c r="F107" t="str">
+        <v>Logged in</v>
+      </c>
+      <c r="G107" t="str">
+        <v>Navigate to /search</v>
+      </c>
+      <c r="H107" t="str">
+        <v>Search input and sidebar visible</v>
+      </c>
+      <c r="I107" t="str">
+        <v>Behaved as expected — assertion passed</v>
+      </c>
+      <c r="J107" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="K107" t="str">
+        <v>High</v>
+      </c>
+      <c r="L107" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="str">
+        <v>TC-M8-SRC-02</v>
+      </c>
+      <c r="B108" t="str">
+        <v>M8 – Discovery</v>
+      </c>
+      <c r="C108" t="str">
+        <v>Search</v>
+      </c>
+      <c r="D108" t="str">
+        <v>Functional</v>
+      </c>
+      <c r="E108" t="str">
+        <v>Keyword search returns results or no-results</v>
+      </c>
+      <c r="F108" t="str">
+        <v>On /search page</v>
+      </c>
+      <c r="G108" t="str">
+        <v>Type "test" → submit</v>
+      </c>
+      <c r="H108" t="str">
+        <v>Results or no-results state shown</v>
+      </c>
+      <c r="I108" t="str">
+        <v>Test failed — Keyword search returned neither results nor a no-results state</v>
+      </c>
+      <c r="J108" t="str">
+        <v>FAIL</v>
+      </c>
+      <c r="K108" t="str">
+        <v>High</v>
+      </c>
+      <c r="L108" t="str">
+        <v>Keyword search returned neither results nor a no-results state</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="str">
+        <v>TC-M8-SRC-03</v>
+      </c>
+      <c r="B109" t="str">
+        <v>M8 – Discovery</v>
+      </c>
+      <c r="C109" t="str">
+        <v>Search</v>
+      </c>
+      <c r="D109" t="str">
+        <v>UI</v>
+      </c>
+      <c r="E109" t="str">
+        <v>Search filter tabs visible</v>
+      </c>
+      <c r="F109" t="str">
+        <v>On /search page</v>
+      </c>
+      <c r="G109" t="str">
+        <v>Check filter tabs</v>
+      </c>
+      <c r="H109" t="str">
+        <v>Tracks/Users/Playlists tabs visible</v>
+      </c>
+      <c r="I109" t="str">
+        <v>Behaved as expected — assertion passed</v>
+      </c>
+      <c r="J109" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="K109" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="L109" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="str">
+        <v>TC-M8-TRD-01</v>
+      </c>
+      <c r="B110" t="str">
+        <v>M8 – Discovery</v>
+      </c>
+      <c r="C110" t="str">
+        <v>Trending</v>
+      </c>
+      <c r="D110" t="str">
+        <v>Functional</v>
+      </c>
+      <c r="E110" t="str">
+        <v>/trending renders charts layout</v>
+      </c>
+      <c r="F110" t="str">
+        <v>Logged in</v>
+      </c>
+      <c r="G110" t="str">
+        <v>Navigate to /trending</v>
+      </c>
+      <c r="H110" t="str">
+        <v>Charts layout renders</v>
+      </c>
+      <c r="I110" t="str">
+        <v>Behaved as expected — assertion passed</v>
+      </c>
+      <c r="J110" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="K110" t="str">
+        <v>High</v>
+      </c>
+      <c r="L110" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="str">
+        <v>TC-M8-TRD-02</v>
+      </c>
+      <c r="B111" t="str">
+        <v>M8 – Discovery</v>
+      </c>
+      <c r="C111" t="str">
+        <v>Trending</v>
+      </c>
+      <c r="D111" t="str">
+        <v>UI</v>
+      </c>
+      <c r="E111" t="str">
+        <v>Trending page shows genre tabs</v>
+      </c>
+      <c r="F111" t="str">
+        <v>On /trending</v>
+      </c>
+      <c r="G111" t="str">
+        <v>Check genre tabs</v>
+      </c>
+      <c r="H111" t="str">
+        <v>Genre tabs visible</v>
+      </c>
+      <c r="I111" t="str">
+        <v>Behaved as expected — assertion passed</v>
+      </c>
+      <c r="J111" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="K111" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="L111" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="str">
+        <v>TC-M8-TRD-03</v>
+      </c>
+      <c r="B112" t="str">
+        <v>M8 – Discovery</v>
+      </c>
+      <c r="C112" t="str">
+        <v>Trending</v>
+      </c>
+      <c r="D112" t="str">
+        <v>Functional</v>
+      </c>
+      <c r="E112" t="str">
+        <v>Trending chart list or loader renders</v>
+      </c>
+      <c r="F112" t="str">
+        <v>On /trending</v>
+      </c>
+      <c r="G112" t="str">
+        <v>Check chart list area</v>
+      </c>
+      <c r="H112" t="str">
+        <v>List, loader, or handled state</v>
+      </c>
+      <c r="I112" t="str">
+        <v>Test failed — Trending chart list/loader did not render a handled state</v>
+      </c>
+      <c r="J112" t="str">
+        <v>FAIL</v>
+      </c>
+      <c r="K112" t="str">
+        <v>High</v>
+      </c>
+      <c r="L112" t="str">
+        <v>Trending chart list/loader did not render a handled state</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="str">
+        <v>TC-M9-DM-01</v>
+      </c>
+      <c r="B113" t="str">
+        <v>M9 – Messaging</v>
+      </c>
+      <c r="C113" t="str">
+        <v>Auth Guard</v>
+      </c>
+      <c r="D113" t="str">
+        <v>Security</v>
+      </c>
+      <c r="E113" t="str">
+        <v>Guest cannot access /messages</v>
+      </c>
+      <c r="F113" t="str">
+        <v>Not logged in</v>
+      </c>
+      <c r="G113" t="str">
+        <v>Navigate to /messages</v>
+      </c>
+      <c r="H113" t="str">
+        <v>Redirected or gated</v>
+      </c>
+      <c r="I113" t="str">
+        <v>Behaved as expected — assertion passed</v>
+      </c>
+      <c r="J113" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="K113" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="L113" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="str">
+        <v>TC-M9-DM-02</v>
+      </c>
+      <c r="B114" t="str">
+        <v>M9 – Messaging</v>
+      </c>
+      <c r="C114" t="str">
+        <v>Messages UI</v>
+      </c>
+      <c r="D114" t="str">
+        <v>Functional</v>
+      </c>
+      <c r="E114" t="str">
+        <v>Messages page renders for authenticated user</v>
+      </c>
+      <c r="F114" t="str">
+        <v>Logged in</v>
+      </c>
+      <c r="G114" t="str">
+        <v>Navigate to /messages</v>
+      </c>
+      <c r="H114" t="str">
+        <v>Messages layout visible</v>
+      </c>
+      <c r="I114" t="str">
+        <v>Behaved as expected — assertion passed</v>
+      </c>
+      <c r="J114" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="K114" t="str">
+        <v>High</v>
+      </c>
+      <c r="L114" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="str">
+        <v>TC-M9-DM-03</v>
+      </c>
+      <c r="B115" t="str">
+        <v>M9 – Messaging</v>
+      </c>
+      <c r="C115" t="str">
+        <v>Compose</v>
+      </c>
+      <c r="D115" t="str">
+        <v>Functional</v>
+      </c>
+      <c r="E115" t="str">
+        <v>Compose button opens recipient input modal</v>
+      </c>
+      <c r="F115" t="str">
+        <v>Logged in, on /messages</v>
+      </c>
+      <c r="G115" t="str">
+        <v>Click compose button</v>
+      </c>
+      <c r="H115" t="str">
+        <v>Recipient modal opens</v>
+      </c>
+      <c r="I115" t="str">
+        <v>Behaved as expected — assertion passed</v>
+      </c>
+      <c r="J115" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="K115" t="str">
+        <v>High</v>
+      </c>
+      <c r="L115" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="str">
+        <v>TC-M9-DM-04</v>
+      </c>
+      <c r="B116" t="str">
+        <v>M9 – Messaging</v>
+      </c>
+      <c r="C116" t="str">
+        <v>Conversation List</v>
+      </c>
+      <c r="D116" t="str">
+        <v>Functional</v>
+      </c>
+      <c r="E116" t="str">
+        <v>Sidebar shows conversations or empty state</v>
+      </c>
+      <c r="F116" t="str">
+        <v>Logged in</v>
+      </c>
+      <c r="G116" t="str">
+        <v>Check sidebar in /messages</v>
+      </c>
+      <c r="H116" t="str">
+        <v>List or empty state</v>
+      </c>
+      <c r="I116" t="str">
+        <v>Behaved as expected — assertion passed</v>
+      </c>
+      <c r="J116" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="K116" t="str">
+        <v>High</v>
+      </c>
+      <c r="L116" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="str">
+        <v>TC-M9-PRV-01</v>
+      </c>
+      <c r="B117" t="str">
+        <v>M9 – Messaging</v>
+      </c>
+      <c r="C117" t="str">
+        <v>Track Sharing</v>
+      </c>
+      <c r="D117" t="str">
+        <v>Functional</v>
+      </c>
+      <c r="E117" t="str">
+        <v>Message input area accepts text</v>
+      </c>
+      <c r="F117" t="str">
+        <v>Conversation open</v>
+      </c>
+      <c r="G117" t="str">
+        <v>Type in message input</v>
+      </c>
+      <c r="H117" t="str">
+        <v>Text accepted</v>
+      </c>
+      <c r="I117" t="str">
+        <v>Behaved as expected — assertion passed</v>
+      </c>
+      <c r="J117" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="K117" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="L117" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="str">
+        <v>TC-M9-STA-01</v>
+      </c>
+      <c r="B118" t="str">
+        <v>M9 – Messaging</v>
+      </c>
+      <c r="C118" t="str">
+        <v>Unread Badge</v>
+      </c>
+      <c r="D118" t="str">
+        <v>UI</v>
+      </c>
+      <c r="E118" t="str">
+        <v>Nav shows unread badge or no badge (both valid)</v>
+      </c>
+      <c r="F118" t="str">
+        <v>Logged in</v>
+      </c>
+      <c r="G118" t="str">
+        <v>Check nav for unread badge</v>
+      </c>
+      <c r="H118" t="str">
+        <v>Badge or no badge — no crash</v>
+      </c>
+      <c r="I118" t="str">
+        <v>Test failed — Messages nav badge state caused an unexpected assertion failure</v>
+      </c>
+      <c r="J118" t="str">
+        <v>FAIL</v>
+      </c>
+      <c r="K118" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="L118" t="str">
+        <v>Messages nav badge state caused an unexpected assertion failure</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="str">
+        <v>TC-M10-ACT-01</v>
+      </c>
+      <c r="B119" t="str">
+        <v>M10 – Notifications</v>
+      </c>
+      <c r="C119" t="str">
+        <v>Notifications</v>
+      </c>
+      <c r="D119" t="str">
+        <v>Functional</v>
+      </c>
+      <c r="E119" t="str">
+        <v>/notifications renders for authenticated user</v>
+      </c>
+      <c r="F119" t="str">
+        <v>Logged in</v>
+      </c>
+      <c r="G119" t="str">
+        <v>Navigate to /notifications</v>
+      </c>
+      <c r="H119" t="str">
+        <v>Page renders</v>
+      </c>
+      <c r="I119" t="str">
+        <v>Behaved as expected — assertion passed</v>
+      </c>
+      <c r="J119" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="K119" t="str">
+        <v>High</v>
+      </c>
+      <c r="L119" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="str">
+        <v>TC-M10-ACT-02</v>
+      </c>
+      <c r="B120" t="str">
+        <v>M10 – Notifications</v>
+      </c>
+      <c r="C120" t="str">
+        <v>Notifications</v>
+      </c>
+      <c r="D120" t="str">
+        <v>Functional</v>
+      </c>
+      <c r="E120" t="str">
+        <v>Page shows items or empty state</v>
+      </c>
+      <c r="F120" t="str">
+        <v>Logged in</v>
+      </c>
+      <c r="G120" t="str">
+        <v>Check notifications list</v>
+      </c>
+      <c r="H120" t="str">
+        <v>Items or empty state</v>
+      </c>
+      <c r="I120" t="str">
+        <v>Behaved as expected — assertion passed</v>
+      </c>
+      <c r="J120" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="K120" t="str">
+        <v>High</v>
+      </c>
+      <c r="L120" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="str">
+        <v>TC-M10-ACT-03</v>
+      </c>
+      <c r="B121" t="str">
+        <v>M10 – Notifications</v>
+      </c>
+      <c r="C121" t="str">
+        <v>Notification Items</v>
+      </c>
+      <c r="D121" t="str">
+        <v>UI</v>
+      </c>
+      <c r="E121" t="str">
+        <v>Items show actor, action, and timestamp</v>
+      </c>
+      <c r="F121" t="str">
+        <v>On /notifications</v>
+      </c>
+      <c r="G121" t="str">
+        <v>Inspect notification items</v>
+      </c>
+      <c r="H121" t="str">
+        <v>Actor, action, timestamp present</v>
+      </c>
+      <c r="I121" t="str">
+        <v>Behaved as expected — assertion passed</v>
+      </c>
+      <c r="J121" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="K121" t="str">
+        <v>High</v>
+      </c>
+      <c r="L121" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="str">
+        <v>TC-M10-ACT-04</v>
+      </c>
+      <c r="B122" t="str">
+        <v>M10 – Notifications</v>
+      </c>
+      <c r="C122" t="str">
+        <v>Unread State</v>
+      </c>
+      <c r="D122" t="str">
+        <v>UI</v>
+      </c>
+      <c r="E122" t="str">
+        <v>Unread items have .unread class when present</v>
+      </c>
+      <c r="F122" t="str">
+        <v>Unread notifications</v>
+      </c>
+      <c r="G122" t="str">
+        <v>Check unread items styling</v>
+      </c>
+      <c r="H122" t="str">
+        <v>.unread class applied</v>
+      </c>
+      <c r="I122" t="str">
+        <v>Behaved as expected — assertion passed</v>
+      </c>
+      <c r="J122" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="K122" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="L122" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="str">
+        <v>TC-M10-STA-01</v>
+      </c>
+      <c r="B123" t="str">
+        <v>M10 – Notifications</v>
+      </c>
+      <c r="C123" t="str">
+        <v>Filtering</v>
+      </c>
+      <c r="D123" t="str">
+        <v>UI</v>
+      </c>
+      <c r="E123" t="str">
+        <v>Filter dropdown visible</v>
+      </c>
+      <c r="F123" t="str">
+        <v>On /notifications</v>
+      </c>
+      <c r="G123" t="str">
+        <v>Check filter dropdown</v>
+      </c>
+      <c r="H123" t="str">
+        <v>Dropdown visible</v>
+      </c>
+      <c r="I123" t="str">
+        <v>Behaved as expected — assertion passed</v>
+      </c>
+      <c r="J123" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="K123" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="L123" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="str">
+        <v>TC-M10-STA-02</v>
+      </c>
+      <c r="B124" t="str">
+        <v>M10 – Notifications</v>
+      </c>
+      <c r="C124" t="str">
+        <v>Mark All Read</v>
+      </c>
+      <c r="D124" t="str">
+        <v>Functional</v>
+      </c>
+      <c r="E124" t="str">
+        <v>Mark-all-read clears unread or is gated</v>
+      </c>
+      <c r="F124" t="str">
+        <v>On /notifications</v>
+      </c>
+      <c r="G124" t="str">
+        <v>Click mark-all-read</v>
+      </c>
+      <c r="H124" t="str">
+        <v>Unread cleared or action gated</v>
+      </c>
+      <c r="I124" t="str">
+        <v>Behaved as expected — assertion passed</v>
+      </c>
+      <c r="J124" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="K124" t="str">
+        <v>High</v>
+      </c>
+      <c r="L124" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="str">
+        <v>TC-M10-STA-03</v>
+      </c>
+      <c r="B125" t="str">
+        <v>M10 – Notifications</v>
+      </c>
+      <c r="C125" t="str">
+        <v>Nav Badge</v>
+      </c>
+      <c r="D125" t="str">
+        <v>UI</v>
+      </c>
+      <c r="E125" t="str">
+        <v>Notification bell visible in global nav</v>
+      </c>
+      <c r="F125" t="str">
+        <v>Logged in</v>
+      </c>
+      <c r="G125" t="str">
+        <v>Check global nav</v>
+      </c>
+      <c r="H125" t="str">
+        <v>Bell/icon visible</v>
+      </c>
+      <c r="I125" t="str">
+        <v>Behaved as expected — assertion passed</v>
+      </c>
+      <c r="J125" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="K125" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="L125" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="str">
+        <v>TC-M11-ADM-01</v>
+      </c>
+      <c r="B126" t="str">
+        <v>M11 – Moderation</v>
+      </c>
+      <c r="C126" t="str">
+        <v>Admin Auth Guard</v>
+      </c>
+      <c r="D126" t="str">
+        <v>Security</v>
+      </c>
+      <c r="E126" t="str">
+        <v>/admin not publicly accessible</v>
+      </c>
+      <c r="F126" t="str">
+        <v>Not admin</v>
+      </c>
+      <c r="G126" t="str">
+        <v>Navigate to /admin as non-admin</v>
+      </c>
+      <c r="H126" t="str">
+        <v>Redirected or 403</v>
+      </c>
+      <c r="I126" t="str">
+        <v>Behaved as expected — assertion passed</v>
+      </c>
+      <c r="J126" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="K126" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="L126" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="str">
+        <v>TC-M11-ADM-02</v>
+      </c>
+      <c r="B127" t="str">
+        <v>M11 – Moderation</v>
+      </c>
+      <c r="C127" t="str">
+        <v>Admin Panel</v>
+      </c>
+      <c r="D127" t="str">
+        <v>Functional</v>
+      </c>
+      <c r="E127" t="str">
+        <v>Admin panel renders nav and track management</v>
+      </c>
+      <c r="F127" t="str">
+        <v>Logged in as admin</v>
+      </c>
+      <c r="G127" t="str">
+        <v>Navigate to /admin</v>
+      </c>
+      <c r="H127" t="str">
+        <v>Nav and track section visible</v>
+      </c>
+      <c r="I127" t="str">
+        <v>Behaved as expected — assertion passed</v>
+      </c>
+      <c r="J127" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="K127" t="str">
+        <v>High</v>
+      </c>
+      <c r="L127" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="str">
+        <v>TC-M11-ADM-03</v>
+      </c>
+      <c r="B128" t="str">
+        <v>M11 – Moderation</v>
+      </c>
+      <c r="C128" t="str">
+        <v>Admin Panel</v>
+      </c>
+      <c r="D128" t="str">
+        <v>Functional</v>
+      </c>
+      <c r="E128" t="str">
+        <v>Moderation section reachable from sidebar</v>
+      </c>
+      <c r="F128" t="str">
+        <v>Logged in as admin</v>
+      </c>
+      <c r="G128" t="str">
+        <v>Click moderation in sidebar</v>
+      </c>
+      <c r="H128" t="str">
+        <v>Moderation section opens</v>
+      </c>
+      <c r="I128" t="str">
+        <v>Behaved as expected — assertion passed</v>
+      </c>
+      <c r="J128" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="K128" t="str">
+        <v>High</v>
+      </c>
+      <c r="L128" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="str">
+        <v>TC-M11-HLT-01</v>
+      </c>
+      <c r="B129" t="str">
+        <v>M11 – Moderation</v>
+      </c>
+      <c r="C129" t="str">
+        <v>Platform Health</v>
+      </c>
+      <c r="D129" t="str">
+        <v>Functional</v>
+      </c>
+      <c r="E129" t="str">
+        <v>Health dashboard renders key metrics</v>
+      </c>
+      <c r="F129" t="str">
+        <v>Logged in as admin</v>
+      </c>
+      <c r="G129" t="str">
+        <v>Navigate to health dashboard</v>
+      </c>
+      <c r="H129" t="str">
+        <v>Metrics/charts rendered</v>
+      </c>
+      <c r="I129" t="str">
+        <v>Behaved as expected — assertion passed</v>
+      </c>
+      <c r="J129" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="K129" t="str">
+        <v>High</v>
+      </c>
+      <c r="L129" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="str">
+        <v>TC-M11-REP-01</v>
+      </c>
+      <c r="B130" t="str">
+        <v>M11 – Moderation</v>
+      </c>
+      <c r="C130" t="str">
+        <v>Report Content</v>
+      </c>
+      <c r="D130" t="str">
+        <v>UI</v>
+      </c>
+      <c r="E130" t="str">
+        <v>Flag icon appears on hover over track card</v>
+      </c>
+      <c r="F130" t="str">
+        <v>On home, logged in</v>
+      </c>
+      <c r="G130" t="str">
+        <v>Hover over a track card</v>
+      </c>
+      <c r="H130" t="str">
+        <v>Flag icon appears</v>
+      </c>
+      <c r="I130" t="str">
+        <v>Behaved as expected — assertion passed</v>
+      </c>
+      <c r="J130" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="K130" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="L130" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="str">
+        <v>TC-M11-REP-02</v>
+      </c>
+      <c r="B131" t="str">
+        <v>M11 – Moderation</v>
+      </c>
+      <c r="C131" t="str">
+        <v>Report Content</v>
+      </c>
+      <c r="D131" t="str">
+        <v>Functional</v>
+      </c>
+      <c r="E131" t="str">
+        <v>Clicking flag opens report modal with reasons</v>
+      </c>
+      <c r="F131" t="str">
+        <v>Hovering track card</v>
+      </c>
+      <c r="G131" t="str">
+        <v>Click flag icon</v>
+      </c>
+      <c r="H131" t="str">
+        <v>Report modal with reasons opens</v>
+      </c>
+      <c r="I131" t="str">
+        <v>Behaved as expected — assertion passed</v>
+      </c>
+      <c r="J131" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="K131" t="str">
+        <v>High</v>
+      </c>
+      <c r="L131" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="str">
+        <v>TC-M11-REP-03</v>
+      </c>
+      <c r="B132" t="str">
+        <v>M11 – Moderation</v>
+      </c>
+      <c r="C132" t="str">
+        <v>Report Content</v>
+      </c>
+      <c r="D132" t="str">
+        <v>Functional</v>
+      </c>
+      <c r="E132" t="str">
+        <v>Submitting report shows confirmation or closes</v>
+      </c>
+      <c r="F132" t="str">
+        <v>Report modal open</v>
+      </c>
+      <c r="G132" t="str">
+        <v>Select reason → submit</v>
+      </c>
+      <c r="H132" t="str">
+        <v>Confirmation or modal closes</v>
+      </c>
+      <c r="I132" t="str">
+        <v>Behaved as expected — assertion passed</v>
+      </c>
+      <c r="J132" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="K132" t="str">
+        <v>High</v>
+      </c>
+      <c r="L132" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="str">
+        <v>TC-M12-PAY-01</v>
+      </c>
+      <c r="B133" t="str">
+        <v>M12 – Premium</v>
+      </c>
+      <c r="C133" t="str">
+        <v>Upgrade CTA</v>
+      </c>
+      <c r="D133" t="str">
+        <v>UI</v>
+      </c>
+      <c r="E133" t="str">
+        <v>Upgrade/pro CTA visible in nav for free users</v>
+      </c>
+      <c r="F133" t="str">
+        <v>Free user logged in</v>
+      </c>
+      <c r="G133" t="str">
+        <v>Check global nav</v>
+      </c>
+      <c r="H133" t="str">
+        <v>Upgrade/Pro CTA visible</v>
+      </c>
+      <c r="I133" t="str">
+        <v>Behaved as expected — assertion passed</v>
+      </c>
+      <c r="J133" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="K133" t="str">
+        <v>High</v>
+      </c>
+      <c r="L133" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="str">
+        <v>TC-M12-PAY-02</v>
+      </c>
+      <c r="B134" t="str">
+        <v>M12 – Premium</v>
+      </c>
+      <c r="C134" t="str">
+        <v>Paywall</v>
+      </c>
+      <c r="D134" t="str">
+        <v>Functional</v>
+      </c>
+      <c r="E134" t="str">
+        <v>Free user at upload limit sees paywall on /upload</v>
+      </c>
+      <c r="F134" t="str">
+        <v>Free user at limit</v>
+      </c>
+      <c r="G134" t="str">
+        <v>Navigate to /upload</v>
+      </c>
+      <c r="H134" t="str">
+        <v>Paywall overlay shown</v>
+      </c>
+      <c r="I134" t="str">
+        <v>Test failed — Free user at upload limit did not see paywall overlay on /upload</v>
+      </c>
+      <c r="J134" t="str">
+        <v>FAIL</v>
+      </c>
+      <c r="K134" t="str">
+        <v>High</v>
+      </c>
+      <c r="L134" t="str">
+        <v>Free user at upload limit did not see paywall overlay on /upload</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="str">
+        <v>TC-M12-PAY-03</v>
+      </c>
+      <c r="B135" t="str">
+        <v>M12 – Premium</v>
+      </c>
+      <c r="C135" t="str">
+        <v>Pricing Page</v>
+      </c>
+      <c r="D135" t="str">
+        <v>Functional</v>
+      </c>
+      <c r="E135" t="str">
+        <v>Guest accessing pricing page handled gracefully</v>
+      </c>
+      <c r="F135" t="str">
+        <v>Not logged in</v>
+      </c>
+      <c r="G135" t="str">
+        <v>Navigate to /upgrade or /pricing</v>
+      </c>
+      <c r="H135" t="str">
+        <v>Page loads gracefully</v>
+      </c>
+      <c r="I135" t="str">
+        <v>Behaved as expected — assertion passed</v>
+      </c>
+      <c r="J135" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="K135" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="L135" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="str">
+        <v>TC-M12-PRK-01</v>
+      </c>
+      <c r="B136" t="str">
+        <v>M12 – Premium</v>
+      </c>
+      <c r="C136" t="str">
+        <v>Pro Perks</v>
+      </c>
+      <c r="D136" t="str">
+        <v>Functional</v>
+      </c>
+      <c r="E136" t="str">
+        <v>Pro user sees download/save option on track page</v>
+      </c>
+      <c r="F136" t="str">
+        <v>Logged in as pro</v>
+      </c>
+      <c r="G136" t="str">
+        <v>Open a track page</v>
+      </c>
+      <c r="H136" t="str">
+        <v>Download or save option present</v>
+      </c>
+      <c r="I136" t="str">
+        <v>Behaved as expected — assertion passed</v>
+      </c>
+      <c r="J136" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="K136" t="str">
+        <v>High</v>
+      </c>
+      <c r="L136" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="str">
+        <v>TC-M12-PRK-02</v>
+      </c>
+      <c r="B137" t="str">
+        <v>M12 – Premium</v>
+      </c>
+      <c r="C137" t="str">
+        <v>Pro Perks</v>
+      </c>
+      <c r="D137" t="str">
+        <v>Functional</v>
+      </c>
+      <c r="E137" t="str">
+        <v>Pro user has no disruptive upgrade prompts</v>
+      </c>
+      <c r="F137" t="str">
+        <v>Logged in as pro</v>
+      </c>
+      <c r="G137" t="str">
+        <v>Browse home page</v>
+      </c>
+      <c r="H137" t="str">
+        <v>No upgrade banners/prompts</v>
+      </c>
+      <c r="I137" t="str">
+        <v>Behaved as expected — assertion passed</v>
+      </c>
+      <c r="J137" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="K137" t="str">
+        <v>High</v>
+      </c>
+      <c r="L137" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="str">
+        <v>TC-M12-PRK-03</v>
+      </c>
+      <c r="B138" t="str">
+        <v>M12 – Premium</v>
+      </c>
+      <c r="C138" t="str">
+        <v>Pro Perks</v>
+      </c>
+      <c r="D138" t="str">
+        <v>Functional</v>
+      </c>
+      <c r="E138" t="str">
+        <v>Pro user can access offline/save without paywall</v>
+      </c>
+      <c r="F138" t="str">
+        <v>Logged in as pro</v>
+      </c>
+      <c r="G138" t="str">
+        <v>Try offline/save feature</v>
+      </c>
+      <c r="H138" t="str">
+        <v>No paywall blocked</v>
+      </c>
+      <c r="I138" t="str">
+        <v>Behaved as expected — assertion passed</v>
+      </c>
+      <c r="J138" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="K138" t="str">
+        <v>High</v>
+      </c>
+      <c r="L138" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="str">
+        <v>TC-M12-SUB-01</v>
+      </c>
+      <c r="B139" t="str">
+        <v>M12 – Premium</v>
+      </c>
+      <c r="C139" t="str">
+        <v>Subscription</v>
+      </c>
+      <c r="D139" t="str">
+        <v>Navigation</v>
+      </c>
+      <c r="E139" t="str">
+        <v>Upgrade CTA navigates to subscription page</v>
+      </c>
+      <c r="F139" t="str">
+        <v>Free user logged in</v>
+      </c>
+      <c r="G139" t="str">
+        <v>Click upgrade CTA</v>
+      </c>
+      <c r="H139" t="str">
+        <v>Navigated to pricing page</v>
+      </c>
+      <c r="I139" t="str">
+        <v>Behaved as expected — assertion passed</v>
+      </c>
+      <c r="J139" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="K139" t="str">
+        <v>High</v>
+      </c>
+      <c r="L139" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="str">
+        <v>TC-M12-SUB-02</v>
+      </c>
+      <c r="B140" t="str">
+        <v>M12 – Premium</v>
+      </c>
+      <c r="C140" t="str">
+        <v>Subscription</v>
+      </c>
+      <c r="D140" t="str">
+        <v>Functional</v>
+      </c>
+      <c r="E140" t="str">
+        <v>Upgrade processes mock payment and reflects pro</v>
+      </c>
+      <c r="F140" t="str">
+        <v>Free user logged in</v>
+      </c>
+      <c r="G140" t="str">
+        <v>Click upgrade → complete payment</v>
+      </c>
+      <c r="H140" t="str">
+        <v>Pro status reflected</v>
+      </c>
+      <c r="I140" t="str">
+        <v>Behaved as expected — assertion passed</v>
+      </c>
+      <c r="J140" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="K140" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="L140" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="str">
+        <v>TC-M12-SUB-03</v>
+      </c>
+      <c r="B141" t="str">
+        <v>M12 – Premium</v>
+      </c>
+      <c r="C141" t="str">
+        <v>Subscription</v>
+      </c>
+      <c r="D141" t="str">
+        <v>UI</v>
+      </c>
+      <c r="E141" t="str">
+        <v>Subscription page lists Free and Pro plans</v>
+      </c>
+      <c r="F141" t="str">
+        <v>On pricing page</v>
+      </c>
+      <c r="G141" t="str">
+        <v>Check plan listing</v>
+      </c>
+      <c r="H141" t="str">
+        <v>Free and Pro plans listed</v>
+      </c>
+      <c r="I141" t="str">
+        <v>Behaved as expected — assertion passed</v>
+      </c>
+      <c r="J141" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="K141" t="str">
+        <v>High</v>
+      </c>
+      <c r="L141" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A2:L2"/>
-  </mergeCells>
+  <autoFilter ref="A1:L141"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L74"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L141"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:E27"/>
   <cols>
-    <col min="1" max="1" width="34.83203125" customWidth="1"/>
+    <col min="1" max="1" width="32.83203125" customWidth="1"/>
     <col min="2" max="2" width="12.83203125" customWidth="1"/>
-    <col min="3" max="3" width="10.83203125" customWidth="1"/>
-    <col min="4" max="4" width="10.83203125" customWidth="1"/>
+    <col min="3" max="3" width="12.83203125" customWidth="1"/>
+    <col min="4" max="4" width="12.83203125" customWidth="1"/>
     <col min="5" max="5" width="14.83203125" customWidth="1"/>
-    <col min="6" max="6" width="12.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>Pulsify — Test Execution Summary</v>
+        <v>PULSIFY — E2E BLACKBOX TESTING SUMMARY</v>
       </c>
       <c r="B1" t="str">
         <v/>
@@ -3329,15 +5808,12 @@
         <v/>
       </c>
       <c r="E1" t="str">
-        <v/>
-      </c>
-      <c r="F1" t="str">
         <v/>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Team 7 | Tester: Mahmoud Attia | Phase 3 | CMPS203 SWE S26</v>
+        <v/>
       </c>
       <c r="B2" t="str">
         <v/>
@@ -3349,15 +5825,12 @@
         <v/>
       </c>
       <c r="E2" t="str">
-        <v/>
-      </c>
-      <c r="F2" t="str">
         <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v/>
+        <v>OVERALL RESULTS</v>
       </c>
       <c r="B3" t="str">
         <v/>
@@ -3369,319 +5842,420 @@
         <v/>
       </c>
       <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
         <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Module</v>
-      </c>
-      <c r="B4" t="str">
-        <v>Total TCs</v>
+        <v>Total Test Cases</v>
+      </c>
+      <c r="B4">
+        <v>140</v>
       </c>
       <c r="C4" t="str">
-        <v>✅ Pass</v>
+        <v/>
       </c>
       <c r="D4" t="str">
-        <v>❌ Fail</v>
+        <v>Pass Rate</v>
       </c>
       <c r="E4" t="str">
-        <v>⚠️ Not Tested</v>
-      </c>
-      <c r="F4" t="str">
-        <v>Pass Rate</v>
+        <v>89.3%</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Module 1 — Auth</v>
+        <v>Passed</v>
       </c>
       <c r="B5">
-        <v>12</v>
-      </c>
-      <c r="C5">
-        <v>7</v>
-      </c>
-      <c r="D5">
-        <v>5</v>
+        <v>125</v>
+      </c>
+      <c r="C5" t="str">
+        <v/>
+      </c>
+      <c r="D5" t="str">
+        <v>Failed</v>
       </c>
       <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5" t="str">
-        <v>58%</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Module 2 — User Profile</v>
+        <v>Skipped</v>
       </c>
       <c r="B6">
-        <v>13</v>
-      </c>
-      <c r="C6">
-        <v>11</v>
-      </c>
-      <c r="D6">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="C6" t="str">
+        <v/>
+      </c>
+      <c r="D6" t="str">
+        <v>Blocked</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
-      <c r="F6" t="str">
-        <v>85%</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Module 3 — Social Graph</v>
-      </c>
-      <c r="B7">
-        <v>10</v>
-      </c>
-      <c r="C7">
-        <v>2</v>
-      </c>
-      <c r="D7">
-        <v>8</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7" t="str">
-        <v>20%</v>
+        <v/>
+      </c>
+      <c r="B7" t="str">
+        <v/>
+      </c>
+      <c r="C7" t="str">
+        <v/>
+      </c>
+      <c r="D7" t="str">
+        <v/>
+      </c>
+      <c r="E7" t="str">
+        <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Module 4 — Audio Tracks</v>
-      </c>
-      <c r="B8">
-        <v>4</v>
-      </c>
-      <c r="C8">
-        <v>0</v>
-      </c>
-      <c r="D8">
-        <v>1</v>
-      </c>
-      <c r="E8">
-        <v>3</v>
-      </c>
-      <c r="F8" t="str">
-        <v>0%</v>
+        <v>MODULE BREAKDOWN</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Total</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="D8" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="E8" t="str">
+        <v>Pass Rate</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Module 5 — Playback</v>
+        <v>M1 – Authentication</v>
       </c>
       <c r="B9">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="D9">
-        <v>9</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="F9" t="str">
-        <v>0%</v>
+        <v>2</v>
+      </c>
+      <c r="E9" t="str">
+        <v>93%</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Module 6 — Engagement</v>
+        <v>M2 – Profile</v>
       </c>
       <c r="B10">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D10">
-        <v>6</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-      <c r="F10" t="str">
-        <v>0%</v>
+        <v>5</v>
+      </c>
+      <c r="E10" t="str">
+        <v>67%</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Module 7 — Playlists</v>
+        <v>M3 – Social</v>
       </c>
       <c r="B11">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D11">
         <v>4</v>
       </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-      <c r="F11" t="str">
-        <v>0%</v>
+      <c r="E11" t="str">
+        <v>67%</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Module 8 — Search &amp; Discovery</v>
+        <v>M4 – Tracks</v>
       </c>
       <c r="B12">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="C12">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="D12">
         <v>0</v>
       </c>
-      <c r="E12">
-        <v>3</v>
-      </c>
-      <c r="F12" t="str">
-        <v>0%</v>
+      <c r="E12" t="str">
+        <v>100%</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Module 9 — Messaging</v>
+        <v>M5 – Playback</v>
       </c>
       <c r="B13">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C13">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D13">
         <v>0</v>
       </c>
-      <c r="E13">
-        <v>2</v>
-      </c>
-      <c r="F13" t="str">
-        <v>0%</v>
+      <c r="E13" t="str">
+        <v>100%</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Module 10 — Notifications</v>
+        <v>M6 – Engagement</v>
       </c>
       <c r="B14">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="C14">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D14">
         <v>0</v>
       </c>
-      <c r="E14">
-        <v>2</v>
-      </c>
-      <c r="F14" t="str">
-        <v>0%</v>
+      <c r="E14" t="str">
+        <v>100%</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Module 11 — Admin</v>
+        <v>M7 – Playlists</v>
       </c>
       <c r="B15">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C15">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D15">
         <v>0</v>
       </c>
-      <c r="E15">
-        <v>2</v>
-      </c>
-      <c r="F15" t="str">
-        <v>0%</v>
+      <c r="E15" t="str">
+        <v>100%</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Module 12 — Premium</v>
+        <v>M8 – Discovery</v>
       </c>
       <c r="B16">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C16">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D16">
-        <v>0</v>
-      </c>
-      <c r="E16">
-        <v>3</v>
-      </c>
-      <c r="F16" t="str">
-        <v>0%</v>
+        <v>2</v>
+      </c>
+      <c r="E16" t="str">
+        <v>80%</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v/>
-      </c>
-      <c r="B17" t="str">
-        <v/>
-      </c>
-      <c r="C17" t="str">
-        <v/>
-      </c>
-      <c r="D17" t="str">
-        <v/>
+        <v>M9 – Messaging</v>
+      </c>
+      <c r="B17">
+        <v>6</v>
+      </c>
+      <c r="C17">
+        <v>5</v>
+      </c>
+      <c r="D17">
+        <v>1</v>
       </c>
       <c r="E17" t="str">
-        <v/>
-      </c>
-      <c r="F17" t="str">
-        <v/>
+        <v>83%</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>TOTAL</v>
+        <v>M10 – Notifications</v>
       </c>
       <c r="B18">
-        <v>70</v>
+        <v>7</v>
       </c>
       <c r="C18">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="D18">
-        <v>35</v>
-      </c>
-      <c r="E18">
-        <v>15</v>
-      </c>
-      <c r="F18" t="str">
-        <v>36%</v>
+        <v>0</v>
+      </c>
+      <c r="E18" t="str">
+        <v>100%</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>M11 – Moderation</v>
+      </c>
+      <c r="B19">
+        <v>7</v>
+      </c>
+      <c r="C19">
+        <v>7</v>
+      </c>
+      <c r="D19">
+        <v>0</v>
+      </c>
+      <c r="E19" t="str">
+        <v>100%</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>M12 – Premium</v>
+      </c>
+      <c r="B20">
+        <v>9</v>
+      </c>
+      <c r="C20">
+        <v>8</v>
+      </c>
+      <c r="D20">
+        <v>1</v>
+      </c>
+      <c r="E20" t="str">
+        <v>89%</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v/>
+      </c>
+      <c r="B21" t="str">
+        <v/>
+      </c>
+      <c r="C21" t="str">
+        <v/>
+      </c>
+      <c r="D21" t="str">
+        <v/>
+      </c>
+      <c r="E21" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>TEST ENVIRONMENT</v>
+      </c>
+      <c r="B22" t="str">
+        <v/>
+      </c>
+      <c r="C22" t="str">
+        <v/>
+      </c>
+      <c r="D22" t="str">
+        <v/>
+      </c>
+      <c r="E22" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>Application URL</v>
+      </c>
+      <c r="B23" t="str">
+        <v>https://pulsify.page</v>
+      </c>
+      <c r="C23" t="str">
+        <v/>
+      </c>
+      <c r="D23" t="str">
+        <v/>
+      </c>
+      <c r="E23" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>Test Framework</v>
+      </c>
+      <c r="B24" t="str">
+        <v>Playwright + Chromium (E2E)</v>
+      </c>
+      <c r="C24" t="str">
+        <v/>
+      </c>
+      <c r="D24" t="str">
+        <v/>
+      </c>
+      <c r="E24" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>Test Date</v>
+      </c>
+      <c r="B25" t="str">
+        <v>2026-05-03</v>
+      </c>
+      <c r="C25" t="str">
+        <v/>
+      </c>
+      <c r="D25" t="str">
+        <v/>
+      </c>
+      <c r="E25" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>Test Team</v>
+      </c>
+      <c r="B26" t="str">
+        <v>QA Team — CMPS203 Project</v>
+      </c>
+      <c r="C26" t="str">
+        <v/>
+      </c>
+      <c r="D26" t="str">
+        <v/>
+      </c>
+      <c r="E26" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>Total Duration</v>
+      </c>
+      <c r="B27" t="str">
+        <v>Full suite (headless)</v>
+      </c>
+      <c r="C27" t="str">
+        <v/>
+      </c>
+      <c r="D27" t="str">
+        <v/>
+      </c>
+      <c r="E27" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:F2"/>
-  </mergeCells>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F18"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E27"/>
   </ignoredErrors>
 </worksheet>
 </file>